--- a/tame_output/ON/bt/strategyON_20240425.xlsx
+++ b/tame_output/ON/bt/strategyON_20240425.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.0%</t>
+          <t>136.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>220.5%</t>
+          <t>220.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-594.3%</t>
+          <t>-596.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-273.7%</t>
+          <t>-274.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.6%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-28.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-169.4%</t>
+          <t>-170.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-309.3%</t>
+          <t>-293.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-221.6%</t>
+          <t>-211.8%</t>
         </is>
       </c>
     </row>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705546</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045694</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.31188830135569</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706671</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.29991811929684</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.295507330201491</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776675</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611694</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078594</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116211</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081562</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425322</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702406</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906222</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567239</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487768</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309721</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096469</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761804</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255781</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860422</v>
+        <v>3.763178672860428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575948</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430982</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077639</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457896</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180805</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879198</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568102</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963413</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192811</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527526</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145932</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966253</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046989</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412096</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144509</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.729142822900694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473594</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978363</v>
+        <v>3.71417556397837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675894</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581285</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734154</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.769650521666918</v>
@@ -46223,10 +46223,10 @@
         <v>1.098186921157932</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8479948207358757</v>
+        <v>-0.6711011044883949</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.260853629225394</v>
+        <v>2.366989858973882</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212291</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.764596792240779</v>
@@ -46246,10 +46246,10 @@
         <v>1.033804690207341</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8479948207358757</v>
+        <v>-0.6711011044883949</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.255799899799253</v>
+        <v>2.361936129547742</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.761919561166094</v>
+        <v>3.778954866460617</v>
       </c>
       <c r="C1944" t="n">
         <v>2.756372567685304</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.327565858861267</v>
+        <v>-4.347861076544103</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.02498979982705</v>
+        <v>1.016871712753916</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8532007578048458</v>
+        <v>-0.6900214665266703</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.244452113002397</v>
+        <v>2.342359687769302</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240425.xlsx
+++ b/tame_output/ON/bt/strategyON_20240425.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.1%</t>
+          <t>136.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-596.4%</t>
+          <t>-594.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-274.5%</t>
+          <t>-273.7%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.7%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-170.9%</t>
+          <t>-171.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-293.0%</t>
+          <t>-291.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-211.8%</t>
+          <t>-211.0%</t>
         </is>
       </c>
     </row>
@@ -46263,16 +46263,16 @@
         <v>2.756372567685304</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.347861076544103</v>
+        <v>-4.327272278950288</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.016871712753916</v>
+        <v>1.025107231791442</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6900214665266703</v>
+        <v>-0.6767441529549064</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.342359687769302</v>
+        <v>2.350326075912361</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240425.xlsx
+++ b/tame_output/ON/bt/strategyON_20240425.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>14.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-80.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.3%</t>
+          <t>116.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>220.6%</t>
+          <t>218.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-594.3%</t>
+          <t>-605.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-273.7%</t>
+          <t>-278.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-36.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-31.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.0%</t>
+          <t>-169.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-291.7%</t>
+          <t>-309.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-211.0%</t>
+          <t>-221.6%</t>
         </is>
       </c>
     </row>
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.31188830135569</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153009</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776676</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.78930753648777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.85615817609647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860428</v>
+        <v>3.763178672860424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180808</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.7235626538792</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568104</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963415</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788095</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527526</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353073</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544782</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145934</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009946</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966258</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412098</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.762643902144511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900694</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417556397837</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460389506759</v>
+        <v>3.746038950675896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695445</v>
+        <v>3.765020747695441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77320672158129</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734156</v>
       </c>
       <c r="C1942" t="n">
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.177767940488098</v>
+        <v>-4.287534394012487</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.098186921157932</v>
+        <v>1.054280339748176</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6711011044883949</v>
+        <v>-0.8479948207358757</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.366989858973882</v>
+        <v>2.260853629225394</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.326089194299227</v>
+        <v>-4.435855647823616</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.033804690207341</v>
+        <v>0.9898981087975851</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6711011044883949</v>
+        <v>-0.8479948207358757</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.361936129547742</v>
+        <v>2.255799899799253</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.778954866460617</v>
+        <v>3.430189535376456</v>
       </c>
       <c r="C1944" t="n">
         <v>2.756372567685304</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.327272278950288</v>
+        <v>-4.437038732474678</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.025107231791442</v>
+        <v>0.9812006503816861</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6767441529549064</v>
+        <v>-0.8536378692023873</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.350326075912361</v>
+        <v>2.244189846163872</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240425.xlsx
+++ b/tame_output/ON/bt/strategyON_20240425.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>49.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-34.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.3%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.1%</t>
+          <t>116.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>218.2%</t>
+          <t>220.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-605.3%</t>
+          <t>-594.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-278.1%</t>
+          <t>-273.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.6%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-31.6%</t>
+          <t>-28.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-169.4%</t>
+          <t>-171.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-309.4%</t>
+          <t>-291.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-221.6%</t>
+          <t>-169.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1944"/>
+  <dimension ref="A1:G1945"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705545</v>
+        <v>3.311607601705546</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045694</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831155</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355691</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279816</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511407</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760745</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706675</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.299918119296842</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201493</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153011</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382196</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911642</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416048</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178247</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006535</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628919</v>
+        <v>3.600034689628923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487776</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858725</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85615817609647</v>
+        <v>3.856158176096478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860431</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575957</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430992</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.7235626538792</v>
+        <v>3.723562653879206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568104</v>
+        <v>3.729966140568111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963415</v>
+        <v>3.782918957963423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192813</v>
+        <v>3.828547911192821</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262051</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389906</v>
+        <v>3.812450103389913</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788098</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635139874918</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.8359544114815</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145934</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009946</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412098</v>
+        <v>3.735835647412108</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144511</v>
+        <v>3.762643902144521</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900689</v>
+        <v>3.729142822900698</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978374</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887707</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675896</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695441</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734156</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.287534394012487</v>
+        <v>-4.177767940488098</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.054280339748176</v>
+        <v>1.098186921157932</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8479948207358757</v>
+        <v>-0.6711011044883949</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.260853629225394</v>
+        <v>2.366989858973882</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.435855647823616</v>
+        <v>-4.326089194299227</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9898981087975851</v>
+        <v>1.033804690207341</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8479948207358757</v>
+        <v>-0.6711011044883949</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.255799899799253</v>
+        <v>2.361936129547742</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,45 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.430189535376456</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.756372567685304</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.437038732474678</v>
+        <v>-4.327272278950288</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9812006503816861</v>
+        <v>1.025107231791442</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8536378692023873</v>
+        <v>-0.6767441529549064</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.244189846163872</v>
+        <v>2.350326075912361</v>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" s="2" t="n">
+        <v>45407</v>
+      </c>
+      <c r="B1945" t="n">
+        <v>3.779929394087074</v>
+      </c>
+      <c r="C1945" t="n">
+        <v>2.771884504389833</v>
+      </c>
+      <c r="D1945" t="n">
+        <v>-4.327272278950288</v>
+      </c>
+      <c r="E1945" t="n">
+        <v>1.025107231791442</v>
+      </c>
+      <c r="F1945" t="n">
+        <v>-0.6767441529549064</v>
+      </c>
+      <c r="G1945" t="n">
+        <v>2.764948301376201</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240425.xlsx
+++ b/tame_output/ON/bt/strategyON_20240425.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-53.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-80.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.3%</t>
+          <t>116.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>220.6%</t>
+          <t>218.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-594.3%</t>
+          <t>-604.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-273.7%</t>
+          <t>-277.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-36.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-171.0%</t>
+          <t>-169.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-291.7%</t>
+          <t>-307.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-169.5%</t>
+          <t>-189.0%</t>
         </is>
       </c>
     </row>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511407</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998564</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757927</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760745</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706675</v>
+        <v>3.298730590706674</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296842</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201493</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153011</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382196</v>
+        <v>3.272760131382195</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911642</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416048</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178247</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006535</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860587</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767401</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792546</v>
+        <v>3.573670449792545</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628923</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487776</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096478</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761811</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255789</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860431</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575957</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430992</v>
+        <v>3.75387899643099</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077648</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457905</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180812</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879206</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568111</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963423</v>
+        <v>3.782918957963421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192821</v>
+        <v>3.828547911192819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262051</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389913</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788098</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527529</v>
+        <v>3.824307657527528</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359544114815</v>
+        <v>3.835954411481498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102784</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712297</v>
+        <v>3.797691308712295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234997</v>
+        <v>3.822323422349968</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412108</v>
+        <v>3.735835647412105</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144521</v>
+        <v>3.762643902144518</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900698</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473604</v>
+        <v>3.743216620473601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978374</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887707</v>
+        <v>3.710903155887704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.765020747695446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.78434037673416</v>
       </c>
       <c r="C1942" t="n">
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.177767940488098</v>
+        <v>-4.281214123289434</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.098186921157932</v>
+        <v>1.056808448037398</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6711011044883949</v>
+        <v>-0.8277144441490136</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.366989858973882</v>
+        <v>2.273021855177511</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.326089194299227</v>
+        <v>-4.429535377100563</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.033804690207341</v>
+        <v>0.9924262170868063</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6711011044883949</v>
+        <v>-0.8277144441490136</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.361936129547742</v>
+        <v>2.267968125751371</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.756372567685304</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.327272278950288</v>
+        <v>-4.430718461751624</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.025107231791442</v>
+        <v>0.9837287586709074</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6767441529549064</v>
+        <v>-0.8333574926155252</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.350326075912361</v>
+        <v>2.25635807211599</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.779929394087074</v>
+        <v>3.418543582004625</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.771884504389833</v>
+        <v>2.577271047678714</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.327272278950288</v>
+        <v>-4.430718461751624</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.025107231791442</v>
+        <v>0.9837287586709074</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6767441529549064</v>
+        <v>-0.8333574926155252</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.764948301376201</v>
+        <v>2.570334844665082</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240425.xlsx
+++ b/tame_output/ON/bt/strategyON_20240425.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-25</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-53.9%</t>
+          <t>-24.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.1%</t>
+          <t>115.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>136.0%</t>
+          <t>135.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-685.6%</t>
+          <t>-680.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.0%</t>
+          <t>-56.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>218.1%</t>
+          <t>220.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-604.6%</t>
+          <t>-593.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.6%</t>
+          <t>-44.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-277.8%</t>
+          <t>-273.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-36.4%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-38.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-29.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-169.4%</t>
+          <t>-169.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-307.3%</t>
+          <t>-304.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-189.0%</t>
+          <t>-159.7%</t>
         </is>
       </c>
     </row>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511407</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998564</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757927</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760745</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706674</v>
+        <v>3.298730590706675</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.299918119296842</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201492</v>
+        <v>3.295507330201493</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153011</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382195</v>
+        <v>3.272760131382196</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.233800325911642</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416048</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.278199702495502</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178247</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006535</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737175</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.9723349004829</v>
+        <v>-10.85097844882709</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.247381294088798</v>
+        <v>-1.198838713426472</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.12178766199094</v>
+        <v>-3.070000977368361</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.268836493223547</v>
+        <v>1.299908503997095</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.89886506881546</v>
+        <v>-10.77750861715964</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.202621659928398</v>
+        <v>-1.154079079266071</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.048317830323492</v>
+        <v>-2.996531145700912</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.328290093717437</v>
+        <v>1.359362104490985</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.073989486202</v>
+        <v>-10.95263303454618</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.258116206135498</v>
+        <v>-1.209573625473172</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.223442247710036</v>
+        <v>-3.171655563087456</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.237770664033028</v>
+        <v>1.268842674806576</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.30844158021649</v>
+        <v>-11.18708512856067</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.35911620864289</v>
+        <v>-1.310573627980564</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.223442247710036</v>
+        <v>-3.171655563087456</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.230551499131432</v>
+        <v>1.26162350990498</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.59624542475373</v>
+        <v>-11.47488897309791</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.480909937231762</v>
+        <v>-1.432367356569435</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.511246092247274</v>
+        <v>-3.459459407624694</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.051197001635113</v>
+        <v>1.08226901240866</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.82606987191755</v>
+        <v>-11.70471342026174</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.571723926258735</v>
+        <v>-1.523181345596409</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.673893629317434</v>
+        <v>-3.622106944694855</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9547242692315727</v>
+        <v>0.9857962800051205</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767401</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.05809879165381</v>
+        <v>-11.936742339998</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.661841765524125</v>
+        <v>-1.613299184861799</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.735906326505857</v>
+        <v>-3.684119641883278</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9202103795476333</v>
+        <v>0.9512823903211811</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792545</v>
+        <v>3.573670449792546</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.006083277685</v>
+        <v>-11.88472682602919</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.637045224250199</v>
+        <v>-1.588502643587873</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.735906326505857</v>
+        <v>-3.684119641883278</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9242007152340341</v>
+        <v>0.955272726007582</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.600034689628923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.14775511940912</v>
+        <v>-12.02639866775331</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.695189187838589</v>
+        <v>-1.646646607176263</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.735906326505857</v>
+        <v>-3.684119641883278</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9227254883352924</v>
+        <v>0.9537974991088403</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.2466618598684</v>
+        <v>-12.12530540821258</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.719698473857427</v>
+        <v>-1.671155893195101</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.834813066965133</v>
+        <v>-3.783026382342553</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8784348542245994</v>
+        <v>0.9095068649981473</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.0475097526313</v>
+        <v>-11.92615330097548</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.653088764609271</v>
+        <v>-1.604546183946944</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.66949054101532</v>
+        <v>-3.61770385639274</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9645772361478047</v>
+        <v>0.9956492469213525</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.82166459991189</v>
+        <v>-11.70030814825607</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.553171630485298</v>
+        <v>-1.504629049822971</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.627563865428156</v>
+        <v>-3.575777180805576</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.9993123145363114</v>
+        <v>1.030384325309859</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.53538978758919</v>
+        <v>-11.41403333593338</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.437522561000161</v>
+        <v>-1.388979980337834</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.627563865428156</v>
+        <v>-3.575777180805576</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.00045145909237</v>
+        <v>1.031523469865918</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.58828507563348</v>
+        <v>-11.46692862397766</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.456046902055768</v>
+        <v>-1.407504321393441</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.62260851933971</v>
+        <v>-3.57082183471713</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.006058440907545</v>
+        <v>1.037130451681093</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.76894809908157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.30437634470473</v>
+        <v>-11.18301989304891</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.336749705445632</v>
+        <v>-1.288207124783304</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.62260851933971</v>
+        <v>-3.57082183471713</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.011792145146182</v>
+        <v>1.04286415591973</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.18895542056663</v>
+        <v>-11.06759896891082</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.300318598184258</v>
+        <v>-1.251776017521932</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.507187595201614</v>
+        <v>-3.455400910579034</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.071307437235174</v>
+        <v>1.102379448008722</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.92511855336256</v>
+        <v>-10.80376210170675</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.204667332615538</v>
+        <v>-1.156124751953211</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.507187595201614</v>
+        <v>-3.455400910579034</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.061423955922267</v>
+        <v>1.092495966695815</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.65787675249417</v>
+        <v>-10.53652030083835</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.099605172767553</v>
+        <v>-1.051062592105226</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.507187595201614</v>
+        <v>-3.455400910579034</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.059589395422893</v>
+        <v>1.090661406196441</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.53457082401595</v>
+        <v>-10.41321437236013</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.050583116349726</v>
+        <v>-1.002040535687399</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.417769924074051</v>
+        <v>-3.365983239451471</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.11293968312597</v>
+        <v>1.144011693899518</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.51061728303999</v>
+        <v>-10.38926083138417</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.040333193813849</v>
+        <v>-0.9917906131515219</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.393816383098094</v>
+        <v>-3.342029698475514</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.127980313857038</v>
+        <v>1.159052324630586</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.789307536487776</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.24655734471719</v>
+        <v>-10.12520089306138</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9479695346464823</v>
+        <v>-0.8994269539841557</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.129756444775297</v>
+        <v>-3.077969760152718</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.273155960688964</v>
+        <v>1.304227971462512</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.539477721212355</v>
+        <v>-9.418121269556538</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6679247189048487</v>
+        <v>-0.6193821382425218</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.129756444775297</v>
+        <v>-3.077969760152718</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.270368927028663</v>
+        <v>1.301440937802211</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858732</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.499293422846165</v>
+        <v>-9.377936971190348</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6515073756705312</v>
+        <v>-0.6029647950082042</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.089572146409107</v>
+        <v>-3.037785461786527</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.294823129936219</v>
+        <v>1.325895140709767</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096478</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.41922362730836</v>
+        <v>-9.297867175652543</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6201126362346523</v>
+        <v>-0.5715700555723253</v>
       </c>
       <c r="F1902" t="n">
-        <v>-3.009502350871303</v>
+        <v>-2.957715666248723</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.342231828479658</v>
+        <v>1.373303839253206</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.185742405078763</v>
+        <v>-9.064385953422946</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5187957185049608</v>
+        <v>-0.4702531378426338</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.776021128641704</v>
+        <v>-2.724234444019124</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.490244990655269</v>
+        <v>1.521317001428818</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255789</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.006033874934889</v>
+        <v>-8.884677423279072</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4498045167603708</v>
+        <v>-0.4012619360980438</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.718849624479008</v>
+        <v>-2.667062939856428</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.521655682839928</v>
+        <v>1.552727693613476</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860431</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.873758401304002</v>
+        <v>-8.752401949648185</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4015268405609889</v>
+        <v>-0.3529842598986619</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.586574150848122</v>
+        <v>-2.534787466225542</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.596388453765487</v>
+        <v>1.627460464539035</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575957</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.683158726630849</v>
+        <v>-8.561802274975031</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3224719100040905</v>
+        <v>-0.2739293293417635</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.395974476174969</v>
+        <v>-2.344187791552389</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.713563319257015</v>
+        <v>1.744635330030563</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.75387899643099</v>
+        <v>3.753878996430992</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.434158927947268</v>
+        <v>-8.31280247629145</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2099656493069992</v>
+        <v>-0.1614230686446727</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.395974476174969</v>
+        <v>-2.344187791552389</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.726469660480674</v>
+        <v>1.757541671254222</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077648</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.539748917720372</v>
+        <v>-8.418392466064555</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3801775748154599</v>
+        <v>-0.3316349941531329</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.501564465948074</v>
+        <v>-2.449777781325494</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.535139737017593</v>
+        <v>1.56621174779114</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457905</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.558483819838969</v>
+        <v>-8.437127368183152</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3391271937858122</v>
+        <v>-0.2905846131234853</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.501564465948074</v>
+        <v>-2.449777781325494</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.583684078894679</v>
+        <v>1.614756089668227</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.41054377843137</v>
+        <v>-8.289187326775552</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3998300999109401</v>
+        <v>-0.3512875192486131</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.481243550039516</v>
+        <v>-2.429456865416936</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.475997705751646</v>
+        <v>1.507069716525194</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.386315142042397</v>
+        <v>-8.26495869038658</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3988526316088294</v>
+        <v>-0.3503100509465025</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.457014913650544</v>
+        <v>-2.405228229027964</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.481820901331551</v>
+        <v>1.512892912105099</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.342766735271706</v>
+        <v>-8.221410283615889</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.388393880995646</v>
+        <v>-0.339851300333319</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.457014913650544</v>
+        <v>-2.405228229027964</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.474860289236458</v>
+        <v>1.505932300010006</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963421</v>
+        <v>3.782918957963423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.100618341817848</v>
+        <v>-7.97926189016203</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2770721692329596</v>
+        <v>-0.2285295885706327</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.457014913650544</v>
+        <v>-2.405228229027964</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.489322643617601</v>
+        <v>1.520394654391149</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192819</v>
+        <v>3.828547911192821</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-8.0373889700495</v>
+        <v>-7.916032518393682</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2572483000664256</v>
+        <v>-0.2087057194040982</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.457014913650544</v>
+        <v>-2.405228229027964</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.483854764076796</v>
+        <v>1.514926774850344</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262051</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.850901277672494</v>
+        <v>-7.729544826016676</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1851551291050462</v>
+        <v>-0.1366125484427192</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.270527221273537</v>
+        <v>-2.218740536650957</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.593245473513577</v>
+        <v>1.624317484287125</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389913</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.829752078769051</v>
+        <v>-7.708395627113233</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1689944713063438</v>
+        <v>-0.1204518906440164</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.249378022370094</v>
+        <v>-2.197591337747514</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.613635971092968</v>
+        <v>1.644707981866516</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788098</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.585986636785607</v>
+        <v>-7.464630185129788</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.07570758616591533</v>
+        <v>-0.02716500550358836</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.249378022370094</v>
+        <v>-2.197591337747514</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.609416679440019</v>
+        <v>1.640488690213566</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527528</v>
+        <v>3.824307657527529</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.321958569592347</v>
+        <v>-7.200602117936528</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.0320279546314044</v>
+        <v>0.08057053529373182</v>
       </c>
       <c r="F1918" t="n">
-        <v>-2.047512623554141</v>
+        <v>-1.99572593893156</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.732660232649607</v>
+        <v>1.763732243423155</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749185</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.072108175643272</v>
+        <v>-6.950751723987453</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1247101871947365</v>
+        <v>0.1732527678570639</v>
       </c>
       <c r="F1919" t="n">
-        <v>-2.047512623554141</v>
+        <v>-1.99572593893156</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.725402307633309</v>
+        <v>1.756474318406857</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481498</v>
+        <v>3.8359544114815</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.768540686639294</v>
+        <v>-6.647184234983475</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2497363063169766</v>
+        <v>0.298278886979304</v>
       </c>
       <c r="F1920" t="n">
-        <v>-2.047512623554141</v>
+        <v>-1.99572593893156</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.729001431153957</v>
+        <v>1.760073441927505</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.69506077778728</v>
+        <v>-6.573704326131461</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2924557759123361</v>
+        <v>0.3409983565746635</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.974032714702126</v>
+        <v>-1.922246030079546</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.78641688251972</v>
+        <v>1.817488893293268</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102784</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.470027778118457</v>
+        <v>-6.348671326462638</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3814894533961621</v>
+        <v>0.4300320340584896</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.748999715033303</v>
+        <v>-1.697213030410723</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.92045715993731</v>
+        <v>1.951529170710859</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353075</v>
+        <v>3.764614304353077</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.25539340048205</v>
+        <v>-6.134036948826231</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4720380055050422</v>
+        <v>0.5205805861673696</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.534365337396896</v>
+        <v>-1.482578652774317</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.053932587573472</v>
+        <v>2.08500459834702</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544784</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.988793043507698</v>
+        <v>-5.867436591851879</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5598724070785783</v>
+        <v>0.6084149877409062</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.534365337396896</v>
+        <v>-1.482578652774317</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.035126846357267</v>
+        <v>2.066198857130815</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712295</v>
+        <v>3.797691308712297</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.748362546702838</v>
+        <v>-5.627006095047019</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6577876824254001</v>
+        <v>0.7063302630877275</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.293934840592036</v>
+        <v>-1.242148155969456</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.181128221065061</v>
+        <v>2.212200231838609</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.505571739053392</v>
+        <v>-5.384215287397573</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7588333193199985</v>
+        <v>0.807375899982326</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.293934840592036</v>
+        <v>-1.242148155969456</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.185057534899881</v>
+        <v>2.216129545673429</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349968</v>
+        <v>3.82232342234997</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.389631889428207</v>
+        <v>-5.268275437772388</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8058878430874126</v>
+        <v>0.85443042374974</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.217113109575912</v>
+        <v>-1.165326424953332</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.231829157426896</v>
+        <v>2.262901168200444</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.146976301005044</v>
+        <v>-5.025619849349225</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8999481496766712</v>
+        <v>0.9484907303389991</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.217113109575912</v>
+        <v>-1.165326424953332</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.228827228646889</v>
+        <v>2.259899239420437</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.926955502968033</v>
+        <v>-4.805599051312214</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9895355059020898</v>
+        <v>1.038078086564417</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.075893264507932</v>
+        <v>-1.024106579885352</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.315138172698291</v>
+        <v>2.346210183471839</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.727706873063224</v>
+        <v>-4.606350421407405</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.085129140665837</v>
+        <v>1.133671721328164</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.075893264507932</v>
+        <v>-1.024106579885352</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.331032355500115</v>
+        <v>2.362104366273662</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.568191769543854</v>
+        <v>-4.446835317888035</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.150081026513887</v>
+        <v>1.198623607176214</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.9163781609885621</v>
+        <v>-0.8645914763659822</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.427887262052038</v>
+        <v>2.458959272825586</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046998</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.423519624444117</v>
+        <v>-4.302163172788298</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.218037987115221</v>
+        <v>1.266580567777549</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7717060158888247</v>
+        <v>-0.7199193312662449</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.524778651673321</v>
+        <v>2.555850662446868</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412105</v>
+        <v>3.735835647412108</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.405750165513161</v>
+        <v>-4.284393713857342</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.140485462774325</v>
+        <v>1.189028043436653</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7539365569578691</v>
+        <v>-0.7021498723352892</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.450780019118616</v>
+        <v>2.481852029892164</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144518</v>
+        <v>3.762643902144521</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.318950667734152</v>
+        <v>-4.197594216078333</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.197605755208495</v>
+        <v>1.246148335870823</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7539365569578691</v>
+        <v>-0.7021498723352892</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.473180512441182</v>
+        <v>2.50425252321473</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900698</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.21925805300514</v>
+        <v>-4.097901601349321</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.237555202473512</v>
+        <v>1.28609778313584</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6542439422288573</v>
+        <v>-0.6024572576062774</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.533068482652001</v>
+        <v>2.564140493425549</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473601</v>
+        <v>3.743216620473604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.28762823932915</v>
+        <v>-4.166271787673331</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.22121405041861</v>
+        <v>1.269756631080937</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.6449682431926423</v>
+        <v>-0.5931815585700625</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.549640824548432</v>
+        <v>2.58071283532198</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978374</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.166211809702673</v>
+        <v>-4.044855358046854</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.260217330901092</v>
+        <v>1.308759911563419</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.6449682431926423</v>
+        <v>-0.5931815585700625</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.540077533180323</v>
+        <v>2.571149543953871</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887704</v>
+        <v>3.710903155887707</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.197204969031379</v>
+        <v>-4.07584851737556</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.072529632209996</v>
+        <v>1.121072212872324</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.6449682431926423</v>
+        <v>-0.5931815585700625</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.36478709822071</v>
+        <v>2.395859108994258</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.021730709238909</v>
+        <v>-3.900374257583091</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.147286568118772</v>
+        <v>1.195829148781099</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.6449682431926423</v>
+        <v>-0.5931815585700625</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.369354330212498</v>
+        <v>2.400426340986046</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695446</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.132666961880158</v>
+        <v>-4.011310510224339</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.10292354094907</v>
+        <v>1.151466121611398</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.6449682431926423</v>
+        <v>-0.5931815585700625</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.369365804099295</v>
+        <v>2.400437814872844</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.335693539423391</v>
+        <v>-4.214337087767572</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.024844295151682</v>
+        <v>1.07338687581401</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.8479948207358757</v>
+        <v>-0.7962081361132959</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.250681242793261</v>
+        <v>2.281753253566809</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434037673416</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.281214123289434</v>
+        <v>-4.166177942356668</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.056808448037398</v>
+        <v>1.102822920410504</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.8277144441490136</v>
+        <v>-0.7962081361132959</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.273021855177511</v>
+        <v>2.291925639998941</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212296</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.429535377100563</v>
+        <v>-4.314499196167797</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9924262170868063</v>
+        <v>1.038440689459913</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.8277144441490136</v>
+        <v>-0.7962081361132959</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.267968125751371</v>
+        <v>2.286871910572802</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.756372567685304</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.430718461751624</v>
+        <v>-4.315682280818859</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9837287586709074</v>
+        <v>1.029743231044014</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8333574926155252</v>
+        <v>-0.8018511845798074</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.25635807211599</v>
+        <v>2.27526185693742</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.418543582004625</v>
+        <v>3.841072152202018</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.577271047678714</v>
+        <v>2.870329718054522</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.430718461751624</v>
+        <v>-4.315682280818859</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9837287586709074</v>
+        <v>1.029743231044014</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8333574926155252</v>
+        <v>-0.8018511845798074</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.570334844665082</v>
+        <v>2.86339351504089</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240425.xlsx
+++ b/tame_output/ON/bt/strategyON_20240425.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.8%</t>
+          <t>116.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-593.1%</t>
+          <t>-581.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-273.2%</t>
+          <t>-268.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-35.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.8%</t>
+          <t>-29.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-304.2%</t>
+          <t>-303.8%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -43704,7 +43704,7 @@
         <v>45295</v>
       </c>
       <c r="B1833" t="n">
-        <v>3.311607601705546</v>
+        <v>3.311607601705545</v>
       </c>
       <c r="C1833" t="n">
         <v>3.12694133299222</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045694</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831155</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355691</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279816</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511407</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998564</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757927</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760745</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706675</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296842</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201493</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153011</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382196</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911642</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416048</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495502</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178247</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006535</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119929</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297754</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737175</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776675</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611699</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.85097844882709</v>
+        <v>-10.84591069646278</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.198838713426472</v>
+        <v>-1.19681161248075</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.070000977368361</v>
+        <v>-3.066516354974471</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.299908503997095</v>
+        <v>1.301999277433429</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.77750861715964</v>
+        <v>-10.77244086479534</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.154079079266071</v>
+        <v>-1.152051978320349</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.996531145700912</v>
+        <v>-2.993046523307023</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.359362104490985</v>
+        <v>1.361452877927319</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.95263303454618</v>
+        <v>-10.94756528218188</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.209573625473172</v>
+        <v>-1.20754652452745</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.171655563087456</v>
+        <v>-3.168170940693567</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.268842674806576</v>
+        <v>1.270933448242909</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.18708512856067</v>
+        <v>-11.18201737619637</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.310573627980564</v>
+        <v>-1.308546527034842</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.171655563087456</v>
+        <v>-3.168170940693567</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.26162350990498</v>
+        <v>1.263714283341313</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.47488897309791</v>
+        <v>-11.46982122073361</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.432367356569435</v>
+        <v>-1.430340255623714</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.459459407624694</v>
+        <v>-3.455974785230805</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.08226901240866</v>
+        <v>1.084359785844994</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860587</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.70471342026174</v>
+        <v>-11.69964566789743</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.523181345596409</v>
+        <v>-1.521154244650687</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.622106944694855</v>
+        <v>-3.618622322300965</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9857962800051205</v>
+        <v>0.9878870534414541</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767401</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.936742339998</v>
+        <v>-11.93167458763369</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.613299184861799</v>
+        <v>-1.611272083916078</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.684119641883278</v>
+        <v>-3.680635019489388</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9512823903211811</v>
+        <v>0.9533731637575147</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792546</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.88472682602919</v>
+        <v>-11.87965907366488</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.588502643587873</v>
+        <v>-1.586475542642151</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.684119641883278</v>
+        <v>-3.680635019489388</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.955272726007582</v>
+        <v>0.9573634994439155</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628923</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.02639866775331</v>
+        <v>-12.021330915389</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.646646607176263</v>
+        <v>-1.644619506230542</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.684119641883278</v>
+        <v>-3.680635019489388</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9537974991088403</v>
+        <v>0.9558882725451738</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410719</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.12530540821258</v>
+        <v>-12.12023765584828</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.671155893195101</v>
+        <v>-1.669128792249379</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.783026382342553</v>
+        <v>-3.779541759948664</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9095068649981473</v>
+        <v>0.9115976384344813</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240579</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.92615330097548</v>
+        <v>-11.92108554861118</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.604546183946944</v>
+        <v>-1.602519083001222</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.61770385639274</v>
+        <v>-3.61421923399885</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9956492469213525</v>
+        <v>0.9977400203576861</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.70030814825607</v>
+        <v>-11.69524039589177</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.504629049822971</v>
+        <v>-1.502601948877249</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.575777180805576</v>
+        <v>-3.572292558411687</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.030384325309859</v>
+        <v>1.032475098746193</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.41403333593338</v>
+        <v>-11.40896558356907</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.388979980337834</v>
+        <v>-1.386952879392112</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.575777180805576</v>
+        <v>-3.572292558411687</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.031523469865918</v>
+        <v>1.033614243302252</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116218</v>
+        <v>3.710931958116211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.46692862397766</v>
+        <v>-11.46186087161336</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.407504321393441</v>
+        <v>-1.405477220447719</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.57082183471713</v>
+        <v>-3.567337212323241</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.037130451681093</v>
+        <v>1.039221225117427</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76894809908157</v>
+        <v>3.768948099081562</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.18301989304891</v>
+        <v>-11.17795214068461</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.288207124783304</v>
+        <v>-1.286180023837583</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.57082183471713</v>
+        <v>-3.567337212323241</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.04286415591973</v>
+        <v>1.044954929356064</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.06759896891082</v>
+        <v>-11.06253121654651</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.251776017521932</v>
+        <v>-1.24974891657621</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.455400910579034</v>
+        <v>-3.451916288185145</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.102379448008722</v>
+        <v>1.104470221445056</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702406</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.80376210170675</v>
+        <v>-10.79869434934244</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.156124751953211</v>
+        <v>-1.154097651007489</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.455400910579034</v>
+        <v>-3.451916288185145</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.092495966695815</v>
+        <v>1.094586740132149</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906222</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.53652030083835</v>
+        <v>-10.53145254847404</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.051062592105226</v>
+        <v>-1.049035491159504</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.455400910579034</v>
+        <v>-3.451916288185145</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.090661406196441</v>
+        <v>1.092752179632775</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468094578195</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.41321437236013</v>
+        <v>-10.40814661999583</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.002040535687399</v>
+        <v>-1.000013434741677</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.365983239451471</v>
+        <v>-3.362498617057582</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.144011693899518</v>
+        <v>1.146102467335852</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567246</v>
+        <v>3.800825778567239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.38926083138417</v>
+        <v>-10.38419307901987</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9917906131515219</v>
+        <v>-0.9897635122058008</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.342029698475514</v>
+        <v>-3.338545076081624</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.159052324630586</v>
+        <v>1.16114309806692</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487776</v>
+        <v>3.789307536487768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.12520089306138</v>
+        <v>-10.12013314069707</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8994269539841557</v>
+        <v>-0.8973998530384337</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.077969760152718</v>
+        <v>-3.074485137758828</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.304227971462512</v>
+        <v>1.306318744898845</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.418121269556538</v>
+        <v>-9.413053517192234</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6193821382425218</v>
+        <v>-0.6173550372967997</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.077969760152718</v>
+        <v>-3.074485137758828</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.301440937802211</v>
+        <v>1.303531711238544</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858732</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.377936971190348</v>
+        <v>-9.372869218826043</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6029647950082042</v>
+        <v>-0.6009376940624822</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.037785461786527</v>
+        <v>-3.034300839392637</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.325895140709767</v>
+        <v>1.3279859141461</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096478</v>
+        <v>3.856158176096469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.297867175652543</v>
+        <v>-9.292799423288239</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5715700555723253</v>
+        <v>-0.5695429546266038</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.957715666248723</v>
+        <v>-2.954231043854833</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.373303839253206</v>
+        <v>1.37539461268954</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761811</v>
+        <v>3.787326853761804</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.064385953422946</v>
+        <v>-9.059318201058641</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4702531378426338</v>
+        <v>-0.4682260368969122</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.724234444019124</v>
+        <v>-2.720749821625235</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.521317001428818</v>
+        <v>1.523407774865151</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255789</v>
+        <v>3.801633547255781</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.884677423279072</v>
+        <v>-8.879609670914768</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4012619360980438</v>
+        <v>-0.3992348351523218</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.667062939856428</v>
+        <v>-2.663578317462539</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.552727693613476</v>
+        <v>1.55481846704981</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860431</v>
+        <v>3.763178672860422</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.752401949648185</v>
+        <v>-8.74733419728388</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3529842598986619</v>
+        <v>-0.3509571589529399</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.534787466225542</v>
+        <v>-2.531302843831652</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.627460464539035</v>
+        <v>1.629551237975368</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575957</v>
+        <v>3.784715218575948</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.561802274975031</v>
+        <v>-8.556734522610727</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2739293293417635</v>
+        <v>-0.2719022283960419</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.344187791552389</v>
+        <v>-2.3407031691585</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.744635330030563</v>
+        <v>1.746726103466897</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430992</v>
+        <v>3.753878996430982</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.31280247629145</v>
+        <v>-8.307734723927146</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1614230686446727</v>
+        <v>-0.1593959676989507</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.344187791552389</v>
+        <v>-2.3407031691585</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.757541671254222</v>
+        <v>1.759632444690556</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077648</v>
+        <v>3.692928280077639</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.418392466064555</v>
+        <v>-8.41332471370025</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3316349941531329</v>
+        <v>-0.3296078932074114</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.449777781325494</v>
+        <v>-2.446293158931604</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.56621174779114</v>
+        <v>1.568302521227474</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457905</v>
+        <v>3.770419008457896</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.437127368183152</v>
+        <v>-8.432059615818847</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2905846131234853</v>
+        <v>-0.2885575121777637</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.449777781325494</v>
+        <v>-2.446293158931604</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.614756089668227</v>
+        <v>1.61684686310456</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180812</v>
+        <v>3.760330111180805</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.289187326775552</v>
+        <v>-8.284119574411248</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3512875192486131</v>
+        <v>-0.3492604183028916</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.429456865416936</v>
+        <v>-2.425972243023046</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.507069716525194</v>
+        <v>1.509160489961528</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879206</v>
+        <v>3.723562653879198</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.26495869038658</v>
+        <v>-8.259890938022275</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3503100509465025</v>
+        <v>-0.3482829500007805</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.405228229027964</v>
+        <v>-2.401743606634074</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.512892912105099</v>
+        <v>1.514983685541433</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568111</v>
+        <v>3.729966140568102</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.221410283615889</v>
+        <v>-8.216342531251584</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.339851300333319</v>
+        <v>-0.3378241993875974</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.405228229027964</v>
+        <v>-2.401743606634074</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.505932300010006</v>
+        <v>1.50802307344634</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963423</v>
+        <v>3.782918957963413</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.97926189016203</v>
+        <v>-7.974194137797726</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2285295885706327</v>
+        <v>-0.2265024876249111</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.405228229027964</v>
+        <v>-2.401743606634074</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.520394654391149</v>
+        <v>1.522485427827483</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192821</v>
+        <v>3.828547911192811</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.916032518393682</v>
+        <v>-7.910964766029378</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2087057194040982</v>
+        <v>-0.2066786184583767</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.405228229027964</v>
+        <v>-2.401743606634074</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.514926774850344</v>
+        <v>1.517017548286678</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262051</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.729544826016676</v>
+        <v>-7.724477073652372</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1366125484427192</v>
+        <v>-0.1345854474969972</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.218740536650957</v>
+        <v>-2.215255914257068</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.624317484287125</v>
+        <v>1.626408257723458</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389913</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.708395627113233</v>
+        <v>-7.703327874748928</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1204518906440164</v>
+        <v>-0.1184247896982948</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.197591337747514</v>
+        <v>-2.194106715353624</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.644707981866516</v>
+        <v>1.64679875530285</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788098</v>
+        <v>3.748324832788088</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.464630185129788</v>
+        <v>-7.459562432765484</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.02716500550358836</v>
+        <v>-0.02513790455786635</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.197591337747514</v>
+        <v>-2.194106715353624</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.640488690213566</v>
+        <v>1.6425794636499</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527529</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.200602117936528</v>
+        <v>-7.195534365572223</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.08057053529373182</v>
+        <v>0.08259763623945382</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.99572593893156</v>
+        <v>-1.992241316537671</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.763732243423155</v>
+        <v>1.765823016859488</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749178</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.950751723987453</v>
+        <v>-6.945683971623149</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1732527678570639</v>
+        <v>0.1752798688027859</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.99572593893156</v>
+        <v>-1.992241316537671</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.756474318406857</v>
+        <v>1.758565091843191</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359544114815</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.647184234983475</v>
+        <v>-6.64211648261917</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.298278886979304</v>
+        <v>0.3003059879250261</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.99572593893156</v>
+        <v>-1.992241316537671</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.760073441927505</v>
+        <v>1.762164215363839</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.573704326131461</v>
+        <v>-6.568636573767156</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3409983565746635</v>
+        <v>0.3430254575203855</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.922246030079546</v>
+        <v>-1.918761407685657</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.817488893293268</v>
+        <v>1.819579666729602</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102784</v>
+        <v>3.773761647102775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.348671326462638</v>
+        <v>-6.343603574098333</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4300320340584896</v>
+        <v>0.4320591350042116</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.697213030410723</v>
+        <v>-1.693728408016834</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.951529170710859</v>
+        <v>1.953619944147192</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353077</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.134036948826231</v>
+        <v>-6.128969196461926</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5205805861673696</v>
+        <v>0.5226076871130916</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.482578652774317</v>
+        <v>-1.479094030380427</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.08500459834702</v>
+        <v>2.087095371783354</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.867436591851879</v>
+        <v>-5.862368839487575</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6084149877409062</v>
+        <v>0.6104420886866277</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.482578652774317</v>
+        <v>-1.479094030380427</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.066198857130815</v>
+        <v>2.068289630567149</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712297</v>
+        <v>3.797691308712288</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.627006095047019</v>
+        <v>-5.621938342682714</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7063302630877275</v>
+        <v>0.7083573640334495</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.242148155969456</v>
+        <v>-1.238663533575567</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.212200231838609</v>
+        <v>2.214291005274942</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.384215287397573</v>
+        <v>-5.379147535033269</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.807375899982326</v>
+        <v>0.809403000928048</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.242148155969456</v>
+        <v>-1.238663533575567</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.216129545673429</v>
+        <v>2.218220319109763</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234997</v>
+        <v>3.82232342234996</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.268275437772388</v>
+        <v>-5.263207685408084</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.85443042374974</v>
+        <v>0.856457524695462</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.165326424953332</v>
+        <v>-1.161841802559443</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.262901168200444</v>
+        <v>2.264991941636777</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.025619849349225</v>
+        <v>-5.02055209698492</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9484907303389991</v>
+        <v>0.9505178312847207</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.165326424953332</v>
+        <v>-1.161841802559443</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.259899239420437</v>
+        <v>2.261990012856771</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.818665376145932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.805599051312214</v>
+        <v>-4.800531298947909</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.038078086564417</v>
+        <v>1.040105187510139</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.024106579885352</v>
+        <v>-1.020621957491463</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.346210183471839</v>
+        <v>2.348300956908173</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009944</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.606350421407405</v>
+        <v>-4.6012826690431</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.133671721328164</v>
+        <v>1.135698822273886</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.024106579885352</v>
+        <v>-1.020621957491463</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.362104366273662</v>
+        <v>2.364195139709996</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.845043810966253</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.446835317888035</v>
+        <v>-4.441767565523731</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.198623607176214</v>
+        <v>1.200650708121936</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8645914763659822</v>
+        <v>-0.8611068539720926</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.458959272825586</v>
+        <v>2.46105004626192</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046989</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.302163172788298</v>
+        <v>-4.297095420423993</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.266580567777549</v>
+        <v>1.268607668723271</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7199193312662449</v>
+        <v>-0.7164347088723553</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.555850662446868</v>
+        <v>2.557941435883202</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412108</v>
+        <v>3.735835647412096</v>
       </c>
       <c r="C1933" t="n">
         <v>2.903141953293337</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.284393713857342</v>
+        <v>-4.279325961493037</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.189028043436653</v>
+        <v>1.191055144382375</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.7021498723352892</v>
+        <v>-0.6986652499413997</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.481852029892164</v>
+        <v>2.483942803328497</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144521</v>
+        <v>3.762643902144509</v>
       </c>
       <c r="C1934" t="n">
         <v>2.925542446615903</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.197594216078333</v>
+        <v>-4.192526463714028</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.246148335870823</v>
+        <v>1.248175436816545</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.7021498723352892</v>
+        <v>-0.6986652499413997</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.50425252321473</v>
+        <v>2.506343296651063</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900698</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.925614847989315</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.097901601349321</v>
+        <v>-4.092833848985016</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.28609778313584</v>
+        <v>1.288124884081561</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.6024572576062774</v>
+        <v>-0.5989726352123879</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.564140493425549</v>
+        <v>2.566231266861883</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473604</v>
+        <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
         <v>2.936621770464017</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.166271787673331</v>
+        <v>-4.161204035309026</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.269756631080937</v>
+        <v>1.271783732026659</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5931815585700625</v>
+        <v>-0.5896969361761729</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.58071283532198</v>
+        <v>2.582803608758314</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978374</v>
+        <v>3.714175563978363</v>
       </c>
       <c r="C1937" t="n">
         <v>2.927058479095908</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.044855358046854</v>
+        <v>-4.03978760568255</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.308759911563419</v>
+        <v>1.310787012509141</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5931815585700625</v>
+        <v>-0.5896969361761729</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.571149543953871</v>
+        <v>2.573240317390205</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887707</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.751768044136295</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.07584851737556</v>
+        <v>-4.070780765011255</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.121072212872324</v>
+        <v>1.123099313818046</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5931815585700625</v>
+        <v>-0.5896969361761729</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.395859108994258</v>
+        <v>2.397949882430592</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.756335276128083</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.900374257583091</v>
+        <v>-3.895306505218786</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.195829148781099</v>
+        <v>1.197856249726821</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5931815585700625</v>
+        <v>-0.5896969361761729</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.400426340986046</v>
+        <v>2.40251711442238</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.76502074769544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.756346750014881</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.011310510224339</v>
+        <v>-4.006242757860035</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.151466121611398</v>
+        <v>1.15349322255712</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5931815585700625</v>
+        <v>-0.5896969361761729</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.400437814872844</v>
+        <v>2.402528588309177</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
         <v>2.759478135234786</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.214337087767572</v>
+        <v>-4.209269335403268</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.07338687581401</v>
+        <v>1.075413976759732</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7962081361132959</v>
+        <v>-0.7927235137194063</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.281753253566809</v>
+        <v>2.283844027003143</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.784340376734154</v>
       </c>
       <c r="C1942" t="n">
         <v>2.769650521666918</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.166177942356668</v>
+        <v>-4.051343736467975</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.102822920410504</v>
+        <v>1.148756602765981</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7962081361132959</v>
+        <v>-0.7927235137194063</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.291925639998941</v>
+        <v>2.294016413435275</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212291</v>
       </c>
       <c r="C1943" t="n">
         <v>2.764596792240779</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.314499196167797</v>
+        <v>-4.199664990279103</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.038440689459913</v>
+        <v>1.08437437181539</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7962081361132959</v>
+        <v>-0.7927235137194063</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.286871910572802</v>
+        <v>2.288962684009135</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786037</v>
       </c>
       <c r="C1944" t="n">
         <v>2.756372567685304</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.315682280818859</v>
+        <v>-4.200848074930164</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.029743231044014</v>
+        <v>1.075676913399491</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8018511845798074</v>
+        <v>-0.7983665621859178</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.27526185693742</v>
+        <v>2.277352630373754</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,19 +46280,19 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.841072152202018</v>
+        <v>3.841072152202008</v>
       </c>
       <c r="C1945" t="n">
         <v>2.870329718054522</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.315682280818859</v>
+        <v>-4.200848074930164</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.029743231044014</v>
+        <v>1.075676913399491</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8018511845798074</v>
+        <v>-0.7983665621859178</v>
       </c>
       <c r="G1945" t="n">
         <v>2.86339351504089</v>

--- a/tame_output/ON/bt/strategyON_20240425.xlsx
+++ b/tame_output/ON/bt/strategyON_20240425.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,12 +819,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-30.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.3%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>116.0%</t>
+          <t>115.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.4%</t>
+          <t>134.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-680.7%</t>
+          <t>-673.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.6%</t>
+          <t>-56.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>220.8%</t>
+          <t>631.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-581.7%</t>
+          <t>-597.4%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-272.7%</t>
+          <t>-266.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-44.2%</t>
+          <t>-43.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-37.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.0%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-268.7%</t>
+          <t>-269.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-348.4%</t>
+          <t>-333.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.7%</t>
+          <t>-37.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-29.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-169.1%</t>
+          <t>-162.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-303.8%</t>
+          <t>-306.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-209.5%</t>
+          <t>-200.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-159.7%</t>
+          <t>-214.1%</t>
         </is>
       </c>
     </row>
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.7497961784502833</v>
+        <v>0.9034601041820449</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.439479989341976</v>
+        <v>3.500945559634681</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.631764624679707</v>
+        <v>1.785428550411469</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.118976717083434</v>
+        <v>4.211175072522492</v>
       </c>
     </row>
     <row r="1835">
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.7492443786084712</v>
+        <v>0.9029083043402327</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.437517105267596</v>
+        <v>3.4989826755603</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.632606388165014</v>
+        <v>1.786270313896775</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.117739611036963</v>
+        <v>4.20993796647602</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.6435574906661714</v>
+        <v>0.797221416397933</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.375067622718123</v>
+        <v>3.436533193010828</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.61804531446233</v>
+        <v>1.771709240194092</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.0888282394428</v>
+        <v>4.181026594881857</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.4615509273432028</v>
+        <v>0.6152148530749644</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.30275413611481</v>
+        <v>3.364219706407515</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.61804531446233</v>
+        <v>1.771709240194092</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.089317378168674</v>
+        <v>4.181515733607731</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4133286604961193</v>
+        <v>0.5669925862278808</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.287545211997643</v>
+        <v>3.349010782290348</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.569823047615247</v>
+        <v>1.723486973347008</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.064464000682091</v>
+        <v>4.156662356121148</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1761971686463242</v>
+        <v>0.3298610943780858</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.227633699755267</v>
+        <v>3.289099270047971</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.569823047615247</v>
+        <v>1.723486973347008</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.099405085179633</v>
+        <v>4.19160344061869</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.1812347593739107</v>
+        <v>0.3348986851056723</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.228226176231639</v>
+        <v>3.289691746524344</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.625467503881564</v>
+        <v>1.779131429613325</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.131369199124761</v>
+        <v>4.223567554563818</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.01860867940927213</v>
+        <v>0.1722726051410337</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.141922125869521</v>
+        <v>3.203387696162226</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.462841423916925</v>
+        <v>1.616505349648687</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.012539932769715</v>
+        <v>4.104738288208772</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.04715871064013993</v>
+        <v>0.1065052150916216</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.116632778980227</v>
+        <v>3.178098349272931</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.462841423916925</v>
+        <v>1.616505349648687</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.013557541900185</v>
+        <v>4.105755897339242</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.06069419441684953</v>
+        <v>0.09296973131491204</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.101846617457298</v>
+        <v>3.163312187750003</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.462841423916925</v>
+        <v>1.616505349648687</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.00418557388794</v>
+        <v>4.096383929326998</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706671</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.1424660948446012</v>
+        <v>0.01119783088716036</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.059220583241436</v>
+        <v>3.120686153534141</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.489876997323062</v>
+        <v>1.643540923054823</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.010489643886861</v>
+        <v>4.102687999325918</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.2096752027164789</v>
+        <v>-0.05601127698471731</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.037102256926387</v>
+        <v>3.098567827219092</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.489876997323062</v>
+        <v>1.643540923054823</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.015254960720563</v>
+        <v>4.10745331615962</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.4172409871080908</v>
+        <v>-0.2635770613763292</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.951900739288983</v>
+        <v>3.013366309581687</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.28231121293145</v>
+        <v>1.435975138663212</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.888540286204837</v>
+        <v>3.980738641643893</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.8349950106549278</v>
+        <v>-0.6813310849231662</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.782726021375311</v>
+        <v>2.844191591668016</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.8645571893846132</v>
+        <v>1.018221115116375</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.635814763581798</v>
+        <v>3.728013119020854</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.056616944213045</v>
+        <v>-0.9029530184812837</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.693943464550986</v>
+        <v>2.75540903484369</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.8270310556972442</v>
+        <v>0.9806949814290056</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.613165299968298</v>
+        <v>3.705363655407355</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.264621002566123</v>
+        <v>-1.110957076834361</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.61563398576368</v>
+        <v>2.677099556056385</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.8270310556972442</v>
+        <v>0.9806949814290056</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.618057444522223</v>
+        <v>3.71025579996128</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.476033423454098</v>
+        <v>-1.322369497722336</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.526150473746478</v>
+        <v>2.587616044039183</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.6156186348092691</v>
+        <v>0.7692825605410305</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.486291448327426</v>
+        <v>3.578489803766483</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.81519180104262</v>
+        <v>-1.661527875310858</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.383571422017519</v>
+        <v>2.445036992310223</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.2764602572207471</v>
+        <v>0.4301241829525084</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.275880721080762</v>
+        <v>3.368079076519819</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.143209022770099</v>
+        <v>-1.989545097038337</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.272702823065295</v>
+        <v>2.334168393358</v>
       </c>
       <c r="F1852" t="n">
-        <v>-0.05155696450673208</v>
+        <v>0.1021069612250293</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.099408677783043</v>
+        <v>3.1916070332221</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.636533894305277</v>
+        <v>-2.482869968573516</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.083471624859792</v>
+        <v>2.144937195152497</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.1565430787463508</v>
+        <v>-0.002879153014589464</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.04451575964784</v>
+        <v>3.136714115086897</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.128918922329374</v>
+        <v>-2.975254996597613</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.887624005693886</v>
+        <v>1.949089575986591</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.6489281067704475</v>
+        <v>-0.4952641810386862</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.750191134877114</v>
+        <v>2.842389490316171</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.514099313259447</v>
+        <v>-3.360435387527685</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.73209438813472</v>
+        <v>1.793559958427425</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.6489281067704475</v>
+        <v>-0.4952641810386862</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.748733673689978</v>
+        <v>2.840932029129034</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.857782086486109</v>
+        <v>-3.704118160754348</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.596390402298671</v>
+        <v>1.657855972591376</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.7568341587976657</v>
+        <v>-0.6031702330659043</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.685759165928263</v>
+        <v>2.77795752136732</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.215432436724457</v>
+        <v>-4.061768510992696</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.44943632085959</v>
+        <v>1.510901891152294</v>
       </c>
       <c r="F1857" t="n">
-        <v>-1.114484509036014</v>
+        <v>-0.9608205833042525</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.467275014441512</v>
+        <v>2.559473369880569</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.524666539720508</v>
+        <v>-4.371002613988747</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.327515606361429</v>
+        <v>1.388981176654133</v>
       </c>
       <c r="F1858" t="n">
-        <v>-1.114484509036014</v>
+        <v>-0.9608205833042525</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.469047941141771</v>
+        <v>2.561246296580828</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.956472332870296</v>
+        <v>-4.802808407138534</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.141126176568918</v>
+        <v>1.202591746861623</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.250902005477281</v>
+        <v>-1.097238079745519</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.373530330744416</v>
+        <v>2.465728686183473</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.191166327002848</v>
+        <v>-5.037502401271087</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.035533353917988</v>
+        <v>1.096998924210693</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.244565738248026</v>
+        <v>-1.090901812516264</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.36561686608406</v>
+        <v>2.457815221523116</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.5268289742333</v>
+        <v>-5.373165048501539</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8998488866817724</v>
+        <v>0.9613144569744767</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.244565738248026</v>
+        <v>-1.090901812516264</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.364197457740024</v>
+        <v>2.456395813179082</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.890455219133614</v>
+        <v>-5.736791293401852</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7608859489558886</v>
+        <v>0.8223515192485928</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.342787375115151</v>
+        <v>-1.18912344938339</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.311752035853991</v>
+        <v>2.403950391293048</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.25558260177236</v>
+        <v>-6.101918676040599</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6140895109062212</v>
+        <v>0.6755550811989255</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.639098159414164</v>
+        <v>-1.485434233682402</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.133220080280415</v>
+        <v>2.225418435719472</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.664171378953039</v>
+        <v>-6.510507453221278</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4494155440487084</v>
+        <v>0.5108811143414131</v>
       </c>
       <c r="F1864" t="n">
-        <v>-2.047686936594842</v>
+        <v>-1.894023010863081</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.886828357986767</v>
+        <v>1.979026713425823</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.077153863094133</v>
+        <v>-6.923489937362372</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2794079828637317</v>
+        <v>0.3408735531564364</v>
       </c>
       <c r="F1865" t="n">
-        <v>-2.047686936594842</v>
+        <v>-1.894023010863081</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.882013790458227</v>
+        <v>1.974212145897284</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.493545737381131</v>
+        <v>-7.339881811649369</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.11084528375781</v>
+        <v>0.1723108540505147</v>
       </c>
       <c r="F1866" t="n">
-        <v>-2.047686936594842</v>
+        <v>-1.894023010863081</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.880007841067105</v>
+        <v>1.972206196506161</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.870222747910975</v>
+        <v>-7.716558822179214</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.02956682978544878</v>
+        <v>0.03189874050725594</v>
       </c>
       <c r="F1867" t="n">
-        <v>-2.047686936594842</v>
+        <v>-1.894023010863081</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.890266531735784</v>
+        <v>1.98246488717484</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.216097569895783</v>
+        <v>-8.062433644164022</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.171817193433677</v>
+        <v>-0.1103516231409722</v>
       </c>
       <c r="F1868" t="n">
-        <v>-2.047686936594842</v>
+        <v>-1.894023010863081</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.886366096881479</v>
+        <v>1.978564452320536</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.378239840358876</v>
+        <v>-8.224575914627115</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2382691815639131</v>
+        <v>-0.1768036112712088</v>
       </c>
       <c r="F1869" t="n">
-        <v>-2.047686936594842</v>
+        <v>-1.894023010863081</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.88477101693648</v>
+        <v>1.976969372375537</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.674901182169075</v>
+        <v>-8.521237256437313</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3531547423587842</v>
+        <v>-0.2916891720660799</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.116430072328721</v>
+        <v>-1.962766146596959</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.847304111425361</v>
+        <v>1.939502466864417</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923087</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.10825029027931</v>
+        <v>-8.954586364547549</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5305206901372816</v>
+        <v>-0.4690551198445769</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.116430072328721</v>
+        <v>-1.962766146596959</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.843277806890958</v>
+        <v>1.935476162330015</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.491251679021941</v>
+        <v>-9.33758775329018</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6838233469559181</v>
+        <v>-0.6223577766632133</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.116430072328721</v>
+        <v>-1.962766146596959</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.843175705569374</v>
+        <v>1.935374061008431</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.648650559235062</v>
+        <v>-9.4949866335033</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7442113830697363</v>
+        <v>-0.6827458127770316</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.273828952541842</v>
+        <v>-2.12016502681008</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.751307893412931</v>
+        <v>1.843506248851988</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.00818088173906</v>
+        <v>-9.854516956007302</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8826732087732867</v>
+        <v>-0.821207638480582</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.273828952541842</v>
+        <v>-2.12016502681008</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.756658196710981</v>
+        <v>1.848856552150038</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.33458091040408</v>
+        <v>-10.18091698467232</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.005317200282115</v>
+        <v>-0.94385162998941</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.600228981206855</v>
+        <v>-2.446565055475094</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.568734199469151</v>
+        <v>1.660932554908208</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776675</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.55372987847827</v>
+        <v>-10.40006595274651</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.089935036890024</v>
+        <v>-1.02846946659732</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.819377949281052</v>
+        <v>-2.665714023549291</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.440286569246401</v>
+        <v>1.532484924685458</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.55003895352186</v>
+        <v>-10.3963750277901</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.088458666907461</v>
+        <v>-1.026993096614756</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.819377949281052</v>
+        <v>-2.665714023549291</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.440286569246401</v>
+        <v>1.532484924685458</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.75429712885173</v>
+        <v>-10.60063320311997</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.164648739920763</v>
+        <v>-1.103183169628059</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.947016893895041</v>
+        <v>-2.79335296816328</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.36921639959665</v>
+        <v>1.461414755035707</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.84591069646278</v>
+        <v>-10.69224677073102</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.19681161248075</v>
+        <v>-1.135346042188046</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.066516354974471</v>
+        <v>-2.91285242924271</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.301999277433429</v>
+        <v>1.394197632872485</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.77244086479534</v>
+        <v>-10.61877693906357</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.152051978320349</v>
+        <v>-1.090586408027645</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.993046523307023</v>
+        <v>-2.839382597575261</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.361452877927319</v>
+        <v>1.453651233366376</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078594</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.94756528218188</v>
+        <v>-10.79390135645012</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.20754652452745</v>
+        <v>-1.146080954234746</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.168170940693567</v>
+        <v>-3.014507014961805</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.270933448242909</v>
+        <v>1.363131803681966</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.18201737619637</v>
+        <v>-11.02835345046461</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.308546527034842</v>
+        <v>-1.247080956742137</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.168170940693567</v>
+        <v>-3.014507014961805</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.263714283341313</v>
+        <v>1.35591263878037</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.46982122073361</v>
+        <v>-11.31615729500185</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.430340255623714</v>
+        <v>-1.368874685331009</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.455974785230805</v>
+        <v>-3.302310859499043</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.084359785844994</v>
+        <v>1.176558141284051</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.69964566789743</v>
+        <v>-11.54598174216567</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.521154244650687</v>
+        <v>-1.459688674357983</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.618622322300965</v>
+        <v>-3.464958396569204</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9878870534414541</v>
+        <v>1.080085408880511</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.93167458763369</v>
+        <v>-11.77801066190193</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.611272083916078</v>
+        <v>-1.549806513623373</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.680635019489388</v>
+        <v>-3.526971093757627</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9533731637575147</v>
+        <v>1.045571519196572</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.87965907366488</v>
+        <v>-11.72599514793312</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.586475542642151</v>
+        <v>-1.525009972349447</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.680635019489388</v>
+        <v>-3.526971093757627</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9573634994439155</v>
+        <v>1.049561854882973</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.021330915389</v>
+        <v>-11.86766698965724</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.644619506230542</v>
+        <v>-1.583153935937837</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.680635019489388</v>
+        <v>-3.526971093757627</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9558882725451738</v>
+        <v>1.048086627984231</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.12023765584828</v>
+        <v>-11.96657373011652</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.669128792249379</v>
+        <v>-1.607663221956674</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.779541759948664</v>
+        <v>-3.625877834216902</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9115976384344813</v>
+        <v>1.003795993873538</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.92108554861118</v>
+        <v>-11.76742162287942</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.602519083001222</v>
+        <v>-1.541053512708518</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.61421923399885</v>
+        <v>-3.460555308267089</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9977400203576861</v>
+        <v>1.089938375796743</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.69524039589177</v>
+        <v>-11.54157647016001</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.502601948877249</v>
+        <v>-1.441136378584545</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.572292558411687</v>
+        <v>-3.418628632679925</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.032475098746193</v>
+        <v>1.12467345418525</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.40896558356907</v>
+        <v>-11.25530165783731</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.386952879392112</v>
+        <v>-1.325487309099409</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.572292558411687</v>
+        <v>-3.418628632679925</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.033614243302252</v>
+        <v>1.125812598741309</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116211</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.46186087161336</v>
+        <v>-11.3081969458816</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.405477220447719</v>
+        <v>-1.344011650155015</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.567337212323241</v>
+        <v>-3.413673286591479</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.039221225117427</v>
+        <v>1.131419580556484</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081562</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.17795214068461</v>
+        <v>-11.02428821495285</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.286180023837583</v>
+        <v>-1.22471445354488</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.567337212323241</v>
+        <v>-3.413673286591479</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.044954929356064</v>
+        <v>1.13715328479512</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425322</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.06253121654651</v>
+        <v>-10.90886729081475</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.24974891657621</v>
+        <v>-1.188283346283506</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.451916288185145</v>
+        <v>-3.298252362453383</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.104470221445056</v>
+        <v>1.196668576884113</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702406</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.79869434934244</v>
+        <v>-10.64503042361068</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.154097651007489</v>
+        <v>-1.092632080714786</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.451916288185145</v>
+        <v>-3.298252362453383</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.094586740132149</v>
+        <v>1.186785095571205</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906222</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.53145254847404</v>
+        <v>-10.37778862274229</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.049035491159504</v>
+        <v>-0.9875699208667998</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.451916288185145</v>
+        <v>-3.298252362453383</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.092752179632775</v>
+        <v>1.184950535071831</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.40814661999583</v>
+        <v>-10.25448269426407</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.000013434741677</v>
+        <v>-0.9385478644489731</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.362498617057582</v>
+        <v>-3.208834691325821</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.146102467335852</v>
+        <v>1.238300822774908</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567239</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.38419307901987</v>
+        <v>-10.23052915328811</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9897635122058008</v>
+        <v>-0.928297941913097</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.338545076081624</v>
+        <v>-3.184881150349863</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.16114309806692</v>
+        <v>1.253341453505977</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487768</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.12013314069707</v>
+        <v>-9.966469214965311</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8973998530384337</v>
+        <v>-0.8359342827457299</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.074485137758828</v>
+        <v>-2.920821212027067</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.306318744898845</v>
+        <v>1.398517100337902</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309721</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.413053517192234</v>
+        <v>-9.259389591460474</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6173550372967997</v>
+        <v>-0.5558894670040959</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.074485137758828</v>
+        <v>-2.920821212027067</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.303531711238544</v>
+        <v>1.395730066677601</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.372869218826043</v>
+        <v>-9.219205293094284</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6009376940624822</v>
+        <v>-0.5394721237697784</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.034300839392637</v>
+        <v>-2.880636913660876</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.3279859141461</v>
+        <v>1.420184269585157</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096469</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.292799423288239</v>
+        <v>-9.139135497556479</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5695429546266038</v>
+        <v>-0.5080773843338999</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.954231043854833</v>
+        <v>-2.800567118123072</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.37539461268954</v>
+        <v>1.467592968128596</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761804</v>
+        <v>3.787326853761811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.059318201058641</v>
+        <v>-8.905654275326881</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4682260368969122</v>
+        <v>-0.4067604666042084</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.720749821625235</v>
+        <v>-2.567085895893473</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.523407774865151</v>
+        <v>1.615606130304208</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255781</v>
+        <v>3.801633547255788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.879609670914768</v>
+        <v>-8.725945745183008</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3992348351523218</v>
+        <v>-0.337769264859618</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.663578317462539</v>
+        <v>-2.509914391730777</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.55481846704981</v>
+        <v>1.647016822488866</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860422</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.053436339386163</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.74733419728388</v>
+        <v>-8.593670271552121</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3509571589529399</v>
+        <v>-0.3843881935484323</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.531302843831652</v>
+        <v>-2.377638918099891</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.629551237975368</v>
+        <v>1.626852988526229</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575948</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.0562514000738</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.556734522610727</v>
+        <v>-8.403070596878967</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2719022283960419</v>
+        <v>-0.3053332629915344</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.3407031691585</v>
+        <v>-2.187039243426738</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.746726103466897</v>
+        <v>1.744027854017757</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430982</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.069157741297459</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.307734723927146</v>
+        <v>-8.154070798195386</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1593959676989507</v>
+        <v>-0.1928270022944432</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.3407031691585</v>
+        <v>-2.187039243426738</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.759632444690556</v>
+        <v>1.756934195241416</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077639</v>
+        <v>3.692928280077646</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>2.94118181169824</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.41332471370025</v>
+        <v>-8.259660787968491</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3296078932074114</v>
+        <v>-0.3630389278029043</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.446293158931604</v>
+        <v>-2.292629233199843</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.568302521227474</v>
+        <v>1.565604271778334</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457896</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>2.989726153575326</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.432059615818847</v>
+        <v>-8.278395690087088</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2885575121777637</v>
+        <v>-0.3219885467732566</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.446293158931604</v>
+        <v>-2.292629233199843</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.61684686310456</v>
+        <v>1.614148613655421</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180805</v>
+        <v>3.760330111180812</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.964743835775355</v>
+        <v>2.869847230887158</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.284119574411248</v>
+        <v>-8.130455648679488</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3492604183028916</v>
+        <v>-0.3826914528983845</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.425972243023046</v>
+        <v>-2.272308317291285</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.509160489961528</v>
+        <v>1.506462240512388</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879198</v>
+        <v>3.723562653879205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.956029849521877</v>
+        <v>2.86113324463368</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.259890938022275</v>
+        <v>-8.106227012290516</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3482829500007805</v>
+        <v>-0.3817139845962734</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.401743606634074</v>
+        <v>-2.248079680902313</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.514983685541433</v>
+        <v>1.512285436092293</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568102</v>
+        <v>3.729966140568108</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.949069237426784</v>
+        <v>2.854172632538587</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.216342531251584</v>
+        <v>-8.031174604915389</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3378241993875974</v>
+        <v>-0.3586536337413158</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.401743606634074</v>
+        <v>-2.248079680902313</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.50802307344634</v>
+        <v>1.505324823997199</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963413</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.963531591807927</v>
+        <v>2.86863498691973</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.974194137797726</v>
+        <v>-7.789026211461531</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2265024876249111</v>
+        <v>-0.2473319219786294</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.401743606634074</v>
+        <v>-2.248079680902313</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.522485427827483</v>
+        <v>1.519787178378343</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192811</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.958063712267122</v>
+        <v>2.863167107378925</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.910964766029378</v>
+        <v>-7.725796839693182</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2066786184583767</v>
+        <v>-0.2275080528120954</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.401743606634074</v>
+        <v>-2.248079680902313</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.517017548286678</v>
+        <v>1.514319298837538</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262042</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.955561806277699</v>
+        <v>2.860665201389502</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.724477073652372</v>
+        <v>-7.539309147316176</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1345854474969972</v>
+        <v>-0.1554148818507159</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.215255914257068</v>
+        <v>-2.061591988525306</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.626408257723458</v>
+        <v>1.623710008274318</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389904</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.963262784515024</v>
+        <v>2.868366179626827</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.703327874748928</v>
+        <v>-7.518159948412733</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1184247896982948</v>
+        <v>-0.1392542240520136</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.194106715353624</v>
+        <v>-2.040442789621863</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.64679875530285</v>
+        <v>1.64410050585371</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.959043492862075</v>
+        <v>2.864146887973878</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.459562432765484</v>
+        <v>-7.274394506429289</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.02513790455786635</v>
+        <v>-0.04596733891158511</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.194106715353624</v>
+        <v>-2.040442789621863</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.6425794636499</v>
+        <v>1.63988121420076</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527521</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.961167806782091</v>
+        <v>2.866271201893894</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.195534365572223</v>
+        <v>-7.010366439236028</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.08259763623945382</v>
+        <v>0.06176820188573506</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.992241316537671</v>
+        <v>-1.83857739080591</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.765823016859488</v>
+        <v>1.763124767410349</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.953909881765793</v>
+        <v>2.859013276877596</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.945683971623149</v>
+        <v>-6.760516045286954</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1752798688027859</v>
+        <v>0.1544504344490671</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.992241316537671</v>
+        <v>-1.83857739080591</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.758565091843191</v>
+        <v>1.755866842394051</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.957509005286441</v>
+        <v>2.862612400398245</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.64211648261917</v>
+        <v>-6.456948556282975</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3003059879250261</v>
+        <v>0.2794765535713073</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.992241316537671</v>
+        <v>-1.83857739080591</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.762164215363839</v>
+        <v>1.759465965914699</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.970836511340995</v>
+        <v>2.875939906452798</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.568636573767156</v>
+        <v>-6.383468647430961</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3430254575203855</v>
+        <v>0.3221960231666667</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.918761407685657</v>
+        <v>-1.765097481953895</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.819579666729602</v>
+        <v>1.816881417280462</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.969856988957292</v>
+        <v>2.874960384069095</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.343603574098333</v>
+        <v>-6.158435647762138</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4320591350042116</v>
+        <v>0.4112297006504928</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.693728408016834</v>
+        <v>-1.540064482285072</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.953619944147192</v>
+        <v>1.950921694698052</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.974551790011609</v>
+        <v>2.879655185123413</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.128969196461926</v>
+        <v>-5.943801270125731</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5226076871130916</v>
+        <v>0.5017782527593728</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.479094030380427</v>
+        <v>-1.325430104648666</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.087095371783354</v>
+        <v>2.084397122334213</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.955746048795405</v>
+        <v>2.860849443907208</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.862368839487575</v>
+        <v>-5.677200913151379</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6104420886866277</v>
+        <v>0.5896126543329094</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.479094030380427</v>
+        <v>-1.325430104648666</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.068289630567149</v>
+        <v>2.065591381118009</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.957489125420282</v>
+        <v>2.862592520532086</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.621938342682714</v>
+        <v>-5.436770416346519</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7083573640334495</v>
+        <v>0.6875279296797308</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.238663533575567</v>
+        <v>-1.084999607843805</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.214291005274942</v>
+        <v>2.211592755825803</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.821589933837683</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.961418439255103</v>
+        <v>2.866521834366906</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.379147535033269</v>
+        <v>-5.193979608697074</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.809403000928048</v>
+        <v>0.7885735665743292</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.238663533575567</v>
+        <v>-1.084999607843805</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.218220319109763</v>
+        <v>2.215522069660623</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.962097023172443</v>
+        <v>2.867200418284246</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.263207685408084</v>
+        <v>-5.078039759071888</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.856457524695462</v>
+        <v>0.8356280903417432</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.161841802559443</v>
+        <v>-1.008177876827681</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.264991941636777</v>
+        <v>2.262293692187638</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972339</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.959095094392436</v>
+        <v>2.864198489504239</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.02055209698492</v>
+        <v>-4.835384170648725</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9505178312847207</v>
+        <v>0.9296883969310021</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.161841802559443</v>
+        <v>-1.008177876827681</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.261990012856771</v>
+        <v>2.259291763407631</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145932</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.96067413140305</v>
+        <v>2.865777526514854</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.800531298947909</v>
+        <v>-4.615363372611714</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.040105187510139</v>
+        <v>1.01927575315642</v>
       </c>
       <c r="F1929" t="n">
-        <v>-1.020621957491463</v>
+        <v>-0.8669580317597012</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.348300956908173</v>
+        <v>2.345602707459033</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009944</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.976568314204874</v>
+        <v>2.881671709316677</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.6012826690431</v>
+        <v>-4.416114742706905</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.135698822273886</v>
+        <v>1.114869387920167</v>
       </c>
       <c r="F1930" t="n">
-        <v>-1.020621957491463</v>
+        <v>-0.8669580317597012</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.364195139709996</v>
+        <v>2.361496890260856</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966253</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.977714158645175</v>
+        <v>2.882817553756979</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.441767565523731</v>
+        <v>-4.256599639187535</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.200650708121936</v>
+        <v>1.179821273768217</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.8611068539720926</v>
+        <v>-0.7074429282403313</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.46105004626192</v>
+        <v>2.45835179681278</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046989</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.987802261206615</v>
+        <v>2.892905656318419</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.297095420423993</v>
+        <v>-4.20864311082244</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.268607668723271</v>
+        <v>1.209091987675695</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.7164347088723553</v>
+        <v>-0.6594863998752358</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.557941435883202</v>
+        <v>2.497213816393277</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412096</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.903141953293337</v>
+        <v>2.80824534840514</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.279325961493037</v>
+        <v>-4.190873651891484</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.191055144382375</v>
+        <v>1.131539463334799</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6986652499413997</v>
+        <v>-0.6417169409442802</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.483942803328497</v>
+        <v>2.423215183838572</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144509</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.925542446615903</v>
+        <v>2.830645841727706</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.192526463714028</v>
+        <v>-4.104074154112475</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.248175436816545</v>
+        <v>1.188659755768969</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6986652499413997</v>
+        <v>-0.6417169409442802</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.506343296651063</v>
+        <v>2.445615677161138</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.729142822900694</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.925614847989315</v>
+        <v>2.830718243101118</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.092833848985016</v>
+        <v>-4.004381539383463</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.288124884081561</v>
+        <v>1.228609203033986</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5989726352123879</v>
+        <v>-0.5420243262152684</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.566231266861883</v>
+        <v>2.505503647371958</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473594</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.936621770464017</v>
+        <v>2.84172516557582</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.161204035309026</v>
+        <v>-4.072751725707473</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.271783732026659</v>
+        <v>1.212268050979084</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5896969361761729</v>
+        <v>-0.5327486271790535</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.582803608758314</v>
+        <v>2.522075989268389</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978363</v>
+        <v>3.71417556397837</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.927058479095908</v>
+        <v>2.832161874207712</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.03978760568255</v>
+        <v>-3.951335296080996</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.310787012509141</v>
+        <v>1.251271331461566</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5896969361761729</v>
+        <v>-0.5327486271790535</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.573240317390205</v>
+        <v>2.51251269790028</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.751768044136295</v>
+        <v>2.656871439248099</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.070780765011255</v>
+        <v>-3.982328455409702</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.123099313818046</v>
+        <v>1.063583632770471</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5896969361761729</v>
+        <v>-0.5327486271790535</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.397949882430592</v>
+        <v>2.337222262940667</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675894</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.756335276128083</v>
+        <v>2.661438671239886</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.895306505218786</v>
+        <v>-3.806854195617233</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.197856249726821</v>
+        <v>1.138340568679246</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5896969361761729</v>
+        <v>-0.5327486271790535</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.40251711442238</v>
+        <v>2.341789494932454</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502074769544</v>
+        <v>3.765020747695447</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.756346750014881</v>
+        <v>2.661450145126684</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.006242757860035</v>
+        <v>-3.917790448258481</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.15349322255712</v>
+        <v>1.093977541509544</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5896969361761729</v>
+        <v>-0.5327486271790535</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.402528588309177</v>
+        <v>2.341800968819252</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581285</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.759478135234786</v>
+        <v>2.664581530346589</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.209269335403268</v>
+        <v>-4.120817025801714</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.075413976759732</v>
+        <v>1.015898295712157</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7927235137194063</v>
+        <v>-0.7357752047222869</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.283844027003143</v>
+        <v>2.223116407513217</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734154</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.769650521666918</v>
+        <v>2.674753916778722</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.051343736467975</v>
+        <v>-3.962891426866422</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.148756602765981</v>
+        <v>1.089240921718406</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7927235137194063</v>
+        <v>-0.7357752047222869</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.294016413435275</v>
+        <v>2.23328879394535</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212291</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.764596792240779</v>
+        <v>2.669700187352582</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.199664990279103</v>
+        <v>-4.11121268067755</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.08437437181539</v>
+        <v>1.024858690767815</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7927235137194063</v>
+        <v>-0.7357752047222869</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.288962684009135</v>
+        <v>2.22823506451921</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786037</v>
+        <v>3.752023923786046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.756372567685304</v>
+        <v>2.661475962797108</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.200848074930164</v>
+        <v>-4.263266639246802</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.075676913399491</v>
+        <v>0.9558128827846395</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7983665621859178</v>
+        <v>-0.8031230842785855</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.277352630373754</v>
+        <v>2.179602112229956</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.841072152202008</v>
+        <v>3.795480554427088</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.870329718054522</v>
+        <v>2.812318357538788</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.200848074930164</v>
+        <v>-4.357928430070483</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.075676913399491</v>
+        <v>1.068790561196847</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7983665621859178</v>
+        <v>-0.8212407295926045</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.86339351504089</v>
+        <v>2.319573919783225</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240425.xlsx
+++ b/tame_output/ON/bt/strategyON_20240425.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>15.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,20 +811,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-04-25</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-31.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-53.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-80.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115.5%</t>
+          <t>116.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.7%</t>
+          <t>136.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-673.0%</t>
+          <t>-701.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-56.0%</t>
+          <t>-57.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>631.0%</t>
+          <t>218.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-597.4%</t>
+          <t>-615.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-275.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-43.7%</t>
+          <t>-45.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-37.3%</t>
+          <t>-123.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-269.3%</t>
+          <t>-299.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-35.4%</t>
+          <t>-39.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-333.1%</t>
+          <t>-348.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-37.8%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.5%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-162.3%</t>
+          <t>-169.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-306.1%</t>
+          <t>-334.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-200.2%</t>
+          <t>-209.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-214.1%</t>
+          <t>-253.6%</t>
         </is>
       </c>
     </row>
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.9034601041820449</v>
+        <v>0.7497961784502833</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.500945559634681</v>
+        <v>3.439479989341976</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.785428550411469</v>
+        <v>1.631764624679707</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.211175072522492</v>
+        <v>4.118976717083434</v>
       </c>
     </row>
     <row r="1835">
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.9029083043402327</v>
+        <v>0.7492443786084712</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.4989826755603</v>
+        <v>3.437517105267596</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.786270313896775</v>
+        <v>1.632606388165014</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.20993796647602</v>
+        <v>4.117739611036963</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.797221416397933</v>
+        <v>0.6435574906661714</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.436533193010828</v>
+        <v>3.375067622718123</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.771709240194092</v>
+        <v>1.61804531446233</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.181026594881857</v>
+        <v>4.0888282394428</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.6152148530749644</v>
+        <v>0.4615509273432028</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.364219706407515</v>
+        <v>3.30275413611481</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.771709240194092</v>
+        <v>1.61804531446233</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.181515733607731</v>
+        <v>4.089317378168674</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.5669925862278808</v>
+        <v>0.4133286604961193</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.349010782290348</v>
+        <v>3.287545211997643</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.723486973347008</v>
+        <v>1.569823047615247</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.156662356121148</v>
+        <v>4.064464000682091</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.3298610943780858</v>
+        <v>0.1761971686463242</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.289099270047971</v>
+        <v>3.227633699755267</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.723486973347008</v>
+        <v>1.569823047615247</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.19160344061869</v>
+        <v>4.099405085179633</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.3348986851056723</v>
+        <v>0.1812347593739107</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.289691746524344</v>
+        <v>3.228226176231639</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.779131429613325</v>
+        <v>1.625467503881564</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.223567554563818</v>
+        <v>4.131369199124761</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1722726051410337</v>
+        <v>0.01860867940927213</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.203387696162226</v>
+        <v>3.141922125869521</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.616505349648687</v>
+        <v>1.462841423916925</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.104738288208772</v>
+        <v>4.012539932769715</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.1065052150916216</v>
+        <v>-0.04715871064013993</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.178098349272931</v>
+        <v>3.116632778980227</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.616505349648687</v>
+        <v>1.462841423916925</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.105755897339242</v>
+        <v>4.013557541900185</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.09296973131491204</v>
+        <v>-0.06069419441684953</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.163312187750003</v>
+        <v>3.101846617457298</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.616505349648687</v>
+        <v>1.462841423916925</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.096383929326998</v>
+        <v>4.00418557388794</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.01119783088716036</v>
+        <v>-0.1424660948446012</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.120686153534141</v>
+        <v>3.059220583241436</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.643540923054823</v>
+        <v>1.489876997323062</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.102687999325918</v>
+        <v>4.010489643886861</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.05601127698471731</v>
+        <v>-0.2096752027164789</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.098567827219092</v>
+        <v>3.037102256926387</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.643540923054823</v>
+        <v>1.489876997323062</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.10745331615962</v>
+        <v>4.015254960720563</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.2635770613763292</v>
+        <v>-0.4172409871080908</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.013366309581687</v>
+        <v>2.951900739288983</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.435975138663212</v>
+        <v>1.28231121293145</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.980738641643893</v>
+        <v>3.888540286204837</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.6813310849231662</v>
+        <v>-0.8349950106549278</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.844191591668016</v>
+        <v>2.782726021375311</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.018221115116375</v>
+        <v>0.8645571893846132</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.728013119020854</v>
+        <v>3.635814763581798</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.9029530184812837</v>
+        <v>-1.056616944213045</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.75540903484369</v>
+        <v>2.693943464550986</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9806949814290056</v>
+        <v>0.8270310556972442</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.705363655407355</v>
+        <v>3.613165299968298</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.110957076834361</v>
+        <v>-1.264621002566123</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.677099556056385</v>
+        <v>2.61563398576368</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9806949814290056</v>
+        <v>0.8270310556972442</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.71025579996128</v>
+        <v>3.618057444522223</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.322369497722336</v>
+        <v>-1.476033423454098</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.587616044039183</v>
+        <v>2.526150473746478</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7692825605410305</v>
+        <v>0.6156186348092691</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.578489803766483</v>
+        <v>3.486291448327426</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.661527875310858</v>
+        <v>-1.81519180104262</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.445036992310223</v>
+        <v>2.383571422017519</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4301241829525084</v>
+        <v>0.2764602572207471</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.368079076519819</v>
+        <v>3.275880721080762</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.989545097038337</v>
+        <v>-2.143209022770099</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.334168393358</v>
+        <v>2.272702823065295</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1021069612250293</v>
+        <v>-0.05155696450673208</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.1916070332221</v>
+        <v>3.099408677783043</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.482869968573516</v>
+        <v>-2.636533894305277</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.144937195152497</v>
+        <v>2.083471624859792</v>
       </c>
       <c r="F1853" t="n">
-        <v>-0.002879153014589464</v>
+        <v>-0.1565430787463508</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.136714115086897</v>
+        <v>3.04451575964784</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.975254996597613</v>
+        <v>-3.128918922329374</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.949089575986591</v>
+        <v>1.887624005693886</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4952641810386862</v>
+        <v>-0.6489281067704475</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.842389490316171</v>
+        <v>2.750191134877114</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.360435387527685</v>
+        <v>-3.514099313259447</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.793559958427425</v>
+        <v>1.73209438813472</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4952641810386862</v>
+        <v>-0.6489281067704475</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.840932029129034</v>
+        <v>2.748733673689978</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.704118160754348</v>
+        <v>-3.857782086486109</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.657855972591376</v>
+        <v>1.596390402298671</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.6031702330659043</v>
+        <v>-0.7568341587976657</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.77795752136732</v>
+        <v>2.685759165928263</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.061768510992696</v>
+        <v>-4.215432436724457</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.510901891152294</v>
+        <v>1.44943632085959</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.9608205833042525</v>
+        <v>-1.114484509036014</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.559473369880569</v>
+        <v>2.467275014441512</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.371002613988747</v>
+        <v>-4.524666539720508</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.388981176654133</v>
+        <v>1.327515606361429</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.9608205833042525</v>
+        <v>-1.114484509036014</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.561246296580828</v>
+        <v>2.469047941141771</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.802808407138534</v>
+        <v>-4.956472332870296</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.202591746861623</v>
+        <v>1.141126176568918</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.097238079745519</v>
+        <v>-1.250902005477281</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.465728686183473</v>
+        <v>2.373530330744416</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.037502401271087</v>
+        <v>-5.191166327002848</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.096998924210693</v>
+        <v>1.035533353917988</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.090901812516264</v>
+        <v>-1.244565738248026</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.457815221523116</v>
+        <v>2.36561686608406</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.373165048501539</v>
+        <v>-5.5268289742333</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9613144569744767</v>
+        <v>0.8998488866817724</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.090901812516264</v>
+        <v>-1.244565738248026</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.456395813179082</v>
+        <v>2.364197457740024</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.736791293401852</v>
+        <v>-5.890455219133614</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8223515192485928</v>
+        <v>0.7608859489558886</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.18912344938339</v>
+        <v>-1.342787375115151</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.403950391293048</v>
+        <v>2.311752035853991</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.101918676040599</v>
+        <v>-6.25558260177236</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6755550811989255</v>
+        <v>0.6140895109062212</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.485434233682402</v>
+        <v>-1.639098159414164</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.225418435719472</v>
+        <v>2.133220080280415</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.510507453221278</v>
+        <v>-6.664171378953039</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5108811143414131</v>
+        <v>0.4494155440487084</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.894023010863081</v>
+        <v>-2.047686936594842</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.979026713425823</v>
+        <v>1.886828357986767</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.923489937362372</v>
+        <v>-7.077153863094133</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3408735531564364</v>
+        <v>0.2794079828637317</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.894023010863081</v>
+        <v>-2.047686936594842</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.974212145897284</v>
+        <v>1.882013790458227</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.339881811649369</v>
+        <v>-7.493545737381131</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1723108540505147</v>
+        <v>0.11084528375781</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.894023010863081</v>
+        <v>-2.047686936594842</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.972206196506161</v>
+        <v>1.880007841067105</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.716558822179214</v>
+        <v>-7.870222747910975</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.03189874050725594</v>
+        <v>-0.02956682978544878</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.894023010863081</v>
+        <v>-2.047686936594842</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.98246488717484</v>
+        <v>1.890266531735784</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.062433644164022</v>
+        <v>-8.216097569895783</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1103516231409722</v>
+        <v>-0.171817193433677</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.894023010863081</v>
+        <v>-2.047686936594842</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.978564452320536</v>
+        <v>1.886366096881479</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.224575914627115</v>
+        <v>-8.378239840358876</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1768036112712088</v>
+        <v>-0.2382691815639131</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.894023010863081</v>
+        <v>-2.047686936594842</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.976969372375537</v>
+        <v>1.88477101693648</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.521237256437313</v>
+        <v>-8.674901182169075</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2916891720660799</v>
+        <v>-0.3531547423587842</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.962766146596959</v>
+        <v>-2.116430072328721</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.939502466864417</v>
+        <v>1.847304111425361</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923087</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.954586364547549</v>
+        <v>-9.10825029027931</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4690551198445769</v>
+        <v>-0.5305206901372816</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.962766146596959</v>
+        <v>-2.116430072328721</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.935476162330015</v>
+        <v>1.843277806890958</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.33758775329018</v>
+        <v>-9.491251679021941</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6223577766632133</v>
+        <v>-0.6838233469559181</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.962766146596959</v>
+        <v>-2.116430072328721</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.935374061008431</v>
+        <v>1.843175705569374</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.4949866335033</v>
+        <v>-9.648650559235062</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6827458127770316</v>
+        <v>-0.7442113830697363</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.12016502681008</v>
+        <v>-2.273828952541842</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.843506248851988</v>
+        <v>1.751307893412931</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737169</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.854516956007302</v>
+        <v>-10.00818088173906</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.821207638480582</v>
+        <v>-0.8826732087732867</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.12016502681008</v>
+        <v>-2.273828952541842</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.848856552150038</v>
+        <v>1.756658196710981</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341312</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.18091698467232</v>
+        <v>-10.33458091040408</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.94385162998941</v>
+        <v>-1.005317200282115</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.446565055475094</v>
+        <v>-2.600228981206855</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.660932554908208</v>
+        <v>1.568734199469151</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776675</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.40006595274651</v>
+        <v>-10.55372987847827</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.02846946659732</v>
+        <v>-1.089935036890024</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.665714023549291</v>
+        <v>-2.819377949281052</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.532484924685458</v>
+        <v>1.440286569246401</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.3963750277901</v>
+        <v>-10.55003895352186</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.026993096614756</v>
+        <v>-1.088458666907461</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.665714023549291</v>
+        <v>-2.819377949281052</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.532484924685458</v>
+        <v>1.440286569246401</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.60063320311997</v>
+        <v>-10.75429712885173</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.103183169628059</v>
+        <v>-1.164648739920763</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.79335296816328</v>
+        <v>-2.947016893895041</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.461414755035707</v>
+        <v>1.36921639959665</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.69224677073102</v>
+        <v>-10.9723349004829</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.135346042188046</v>
+        <v>-1.247381294088798</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.91285242924271</v>
+        <v>-3.12178766199094</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.394197632872485</v>
+        <v>1.268836493223547</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.61877693906357</v>
+        <v>-11.05635025618651</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.090586408027645</v>
+        <v>-1.265615734876818</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.839382597575261</v>
+        <v>-3.205803017694543</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.453651233366376</v>
+        <v>1.233798981294806</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.79390135645012</v>
+        <v>-11.23147467357305</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.146080954234746</v>
+        <v>-1.321110281083919</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.014507014961805</v>
+        <v>-3.380927435081087</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.363131803681966</v>
+        <v>1.143279551610397</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.02835345046461</v>
+        <v>-11.46592676758754</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.247080956742137</v>
+        <v>-1.422110283591311</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.014507014961805</v>
+        <v>-3.380927435081087</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.35591263878037</v>
+        <v>1.136060386708801</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.31615729500185</v>
+        <v>-11.75373061212478</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.368874685331009</v>
+        <v>-1.543904012180182</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.302310859499043</v>
+        <v>-3.668731279618325</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.176558141284051</v>
+        <v>0.9567058892124818</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.54598174216567</v>
+        <v>-11.9835550592886</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.459688674357983</v>
+        <v>-1.634718001207156</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.464958396569204</v>
+        <v>-3.831378816688486</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.080085408880511</v>
+        <v>0.8602331568089419</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.77801066190193</v>
+        <v>-12.21558397902487</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.549806513623373</v>
+        <v>-1.724835840472546</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.526971093757627</v>
+        <v>-3.893391513876909</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.045571519196572</v>
+        <v>0.8257192671250024</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.72599514793312</v>
+        <v>-12.16356846505605</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.525009972349447</v>
+        <v>-1.70003929919862</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.526971093757627</v>
+        <v>-3.893391513876909</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.049561854882973</v>
+        <v>0.8297096028114033</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.86766698965724</v>
+        <v>-12.30524030678017</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.583153935937837</v>
+        <v>-1.75818326278701</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.526971093757627</v>
+        <v>-3.893391513876909</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.048086627984231</v>
+        <v>0.8282343759126616</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.96657373011652</v>
+        <v>-12.40414704723945</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.607663221956674</v>
+        <v>-1.782692548805847</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.625877834216902</v>
+        <v>-3.992298254336184</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.003795993873538</v>
+        <v>0.7839437418019686</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240578</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.76742162287942</v>
+        <v>-12.20499494000235</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.541053512708518</v>
+        <v>-1.716082839557691</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.460555308267089</v>
+        <v>-3.826975728386371</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.089938375796743</v>
+        <v>0.8700861237251738</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.54157647016001</v>
+        <v>-11.97914978728294</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.441136378584545</v>
+        <v>-1.616165705433719</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.418628632679925</v>
+        <v>-3.785049052799208</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.12467345418525</v>
+        <v>0.9048212021136806</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.25530165783731</v>
+        <v>-11.69287497496024</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.325487309099409</v>
+        <v>-1.500516635948582</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.418628632679925</v>
+        <v>-3.785049052799208</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.125812598741309</v>
+        <v>0.9059603466697395</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.3081969458816</v>
+        <v>-11.74577026300453</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.344011650155015</v>
+        <v>-1.519040977004188</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.413673286591479</v>
+        <v>-3.780093706710761</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.131419580556484</v>
+        <v>0.9115673284849146</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081562</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.02428821495285</v>
+        <v>-11.46186153207578</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.22471445354488</v>
+        <v>-1.399743780394052</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.413673286591479</v>
+        <v>-3.780093706710761</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.13715328479512</v>
+        <v>0.9173010327235511</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.90886729081475</v>
+        <v>-11.34644060793769</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.188283346283506</v>
+        <v>-1.363312673132679</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.298252362453383</v>
+        <v>-3.664672782572666</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.196668576884113</v>
+        <v>0.9768163248125434</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702406</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.64503042361068</v>
+        <v>-11.08260374073362</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.092632080714786</v>
+        <v>-1.267661407563959</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.298252362453383</v>
+        <v>-3.664672782572666</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.186785095571205</v>
+        <v>0.9669328434996358</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906222</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.37778862274229</v>
+        <v>-10.81536193986522</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9875699208667998</v>
+        <v>-1.162599247715974</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.298252362453383</v>
+        <v>-3.664672782572666</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.184950535071831</v>
+        <v>0.9650982830002621</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.25448269426407</v>
+        <v>-10.692056011387</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.9385478644489731</v>
+        <v>-1.113577191298147</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.208834691325821</v>
+        <v>-3.575255111445103</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.238300822774908</v>
+        <v>1.018448570703339</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.23052915328811</v>
+        <v>-10.66810247041104</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.928297941913097</v>
+        <v>-1.10332726876227</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.184881150349863</v>
+        <v>-3.551301570469145</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.253341453505977</v>
+        <v>1.033489201434407</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.966469214965311</v>
+        <v>-10.40404253208824</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8359342827457299</v>
+        <v>-1.010963609594903</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.920821212027067</v>
+        <v>-3.287241632146349</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.398517100337902</v>
+        <v>1.178664848266333</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.259389591460474</v>
+        <v>-9.696962908583407</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5558894670040959</v>
+        <v>-0.7309187938532693</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.920821212027067</v>
+        <v>-3.287241632146349</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.395730066677601</v>
+        <v>1.175877814606032</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.219205293094284</v>
+        <v>-9.656778610217216</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5394721237697784</v>
+        <v>-0.7145014506189518</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.880636913660876</v>
+        <v>-3.247057333780158</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.420184269585157</v>
+        <v>1.200332017513588</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.139135497556479</v>
+        <v>-9.576708814679412</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5080773843338999</v>
+        <v>-0.6831067111830729</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.800567118123072</v>
+        <v>-3.166987538242354</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.467592968128596</v>
+        <v>1.247740716057027</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761811</v>
+        <v>3.787326853761804</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.905654275326881</v>
+        <v>-9.343227592449814</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4067604666042084</v>
+        <v>-0.5817897934533813</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.567085895893473</v>
+        <v>-2.933506316012755</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.615606130304208</v>
+        <v>1.395753878232639</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255788</v>
+        <v>3.801633547255781</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.725945745183008</v>
+        <v>-9.163519062305941</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.337769264859618</v>
+        <v>-0.5127985917087914</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.509914391730777</v>
+        <v>-2.87633481185006</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.647016822488866</v>
+        <v>1.427164570417297</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860422</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.053436339386163</v>
+        <v>3.047294589076207</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.593670271552121</v>
+        <v>-9.101415406638605</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3843881935484323</v>
+        <v>-0.5936279978929822</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.377638918099891</v>
+        <v>-2.814231156182724</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.626852988526229</v>
+        <v>1.358755895366573</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575947</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.0562514000738</v>
+        <v>3.050109649763844</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.403070596878967</v>
+        <v>-8.910815731965451</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3053332629915344</v>
+        <v>-0.5145730673360838</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.187039243426738</v>
+        <v>-2.623631481509571</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.744027854017757</v>
+        <v>1.475930760858102</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430982</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.069157741297459</v>
+        <v>3.063015990987503</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.154070798195386</v>
+        <v>-8.66181593328187</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1928270022944432</v>
+        <v>-0.4020668066389925</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.187039243426738</v>
+        <v>-2.623631481509571</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.756934195241416</v>
+        <v>1.488837102081761</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077646</v>
+        <v>3.692928280077638</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.94118181169824</v>
+        <v>2.935040061388284</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.259660787968491</v>
+        <v>-8.767405923054975</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3630389278029043</v>
+        <v>-0.5722787321474536</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.292629233199843</v>
+        <v>-2.729221471282675</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.565604271778334</v>
+        <v>1.297507178618679</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457895</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.989726153575326</v>
+        <v>2.98358440326537</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.278395690087088</v>
+        <v>-8.786140825173572</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3219885467732566</v>
+        <v>-0.531228351117806</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.292629233199843</v>
+        <v>-2.729221471282675</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.614148613655421</v>
+        <v>1.346051520495765</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180812</v>
+        <v>3.760330111180803</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.869847230887158</v>
+        <v>2.863705480577202</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.130455648679488</v>
+        <v>-8.638200783765972</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3826914528983845</v>
+        <v>-0.5919312572429338</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.272308317291285</v>
+        <v>-2.708900555374118</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.506462240512388</v>
+        <v>1.238365147352732</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879205</v>
+        <v>3.723562653879196</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.86113324463368</v>
+        <v>2.854991494323724</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.106227012290516</v>
+        <v>-8.613972147377</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3817139845962734</v>
+        <v>-0.5909537889408232</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.248079680902313</v>
+        <v>-2.684671918985146</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.512285436092293</v>
+        <v>1.244188342932637</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568108</v>
+        <v>3.7299661405681</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.854172632538587</v>
+        <v>2.848030882228631</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.031174604915389</v>
+        <v>-8.570423740606309</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3586536337413158</v>
+        <v>-0.5804950383276397</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.248079680902313</v>
+        <v>-2.684671918985146</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.505324823997199</v>
+        <v>1.237227730837544</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963411</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.86863498691973</v>
+        <v>2.862493236609774</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.789026211461531</v>
+        <v>-8.32827534715245</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2473319219786294</v>
+        <v>-0.4691733265649534</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.248079680902313</v>
+        <v>-2.684671918985146</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.519787178378343</v>
+        <v>1.251690085218687</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.82854791119281</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.863167107378925</v>
+        <v>2.857025357068969</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.725796839693182</v>
+        <v>-8.265045975384103</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2275080528120954</v>
+        <v>-0.4493494573984194</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.248079680902313</v>
+        <v>-2.684671918985146</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.514319298837538</v>
+        <v>1.246222205677882</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.82804935326204</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.860665201389502</v>
+        <v>2.854523451079546</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.539309147316176</v>
+        <v>-8.078558283007096</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1554148818507159</v>
+        <v>-0.3772562864370399</v>
       </c>
       <c r="F1915" t="n">
-        <v>-2.061591988525306</v>
+        <v>-2.498184226608139</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.623710008274318</v>
+        <v>1.355612915114663</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389902</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.868366179626827</v>
+        <v>2.862224429316871</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.518159948412733</v>
+        <v>-8.057409084103654</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1392542240520136</v>
+        <v>-0.3610956286383376</v>
       </c>
       <c r="F1916" t="n">
-        <v>-2.040442789621863</v>
+        <v>-2.477035027704696</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.64410050585371</v>
+        <v>1.376003412694054</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788087</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.864146887973878</v>
+        <v>2.858005137663922</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.274394506429289</v>
+        <v>-7.813643642120209</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.04596733891158511</v>
+        <v>-0.2678087434979091</v>
       </c>
       <c r="F1917" t="n">
-        <v>-2.040442789621863</v>
+        <v>-2.477035027704696</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.63988121420076</v>
+        <v>1.371784121041105</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527519</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.866271201893894</v>
+        <v>2.860129451583938</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.010366439236028</v>
+        <v>-7.54961557492695</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.06176820188573506</v>
+        <v>-0.1600732027005893</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.83857739080591</v>
+        <v>-2.275169628888742</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.763124767410349</v>
+        <v>1.495027674250693</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749177</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.859013276877596</v>
+        <v>2.85287152656764</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.760516045286954</v>
+        <v>-7.299765180977875</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1544504344490671</v>
+        <v>-0.06739097013725726</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.83857739080591</v>
+        <v>-2.275169628888742</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.755866842394051</v>
+        <v>1.487769749234395</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.83595441148149</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.862612400398245</v>
+        <v>2.856470650088289</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.456948556282975</v>
+        <v>-6.996197691973896</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2794765535713073</v>
+        <v>0.0576351489849829</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.83857739080591</v>
+        <v>-2.275169628888742</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.759465965914699</v>
+        <v>1.491368872755044</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862979</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.875939906452798</v>
+        <v>2.869798156142843</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.383468647430961</v>
+        <v>-6.922717783121882</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3221960231666667</v>
+        <v>0.1003546185803423</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.765097481953895</v>
+        <v>-2.201689720036728</v>
       </c>
       <c r="G1921" t="n">
-        <v>1.816881417280462</v>
+        <v>1.548784324120806</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102774</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.874960384069095</v>
+        <v>2.868818633759139</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.158435647762138</v>
+        <v>-6.69768478345306</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4112297006504928</v>
+        <v>0.1893882960641684</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.540064482285072</v>
+        <v>-1.976656720367905</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.950921694698052</v>
+        <v>1.682824601538397</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353065</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.879655185123413</v>
+        <v>2.873513434813457</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.943801270125731</v>
+        <v>-6.483050405816653</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5017782527593728</v>
+        <v>0.2799368481730484</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.325430104648666</v>
+        <v>-1.762022342731498</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.084397122334213</v>
+        <v>1.816300029174558</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544774</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.860849443907208</v>
+        <v>2.854707693597252</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.677200913151379</v>
+        <v>-6.216450048842301</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5896126543329094</v>
+        <v>0.3677712497465846</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.325430104648666</v>
+        <v>-1.762022342731498</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.065591381118009</v>
+        <v>1.797494287958354</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712286</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.862592520532086</v>
+        <v>2.85645077022213</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.436770416346519</v>
+        <v>-5.976019552037441</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6875279296797308</v>
+        <v>0.4656865250934064</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.084999607843805</v>
+        <v>-1.521591845926638</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.211592755825803</v>
+        <v>1.943495662666147</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837683</v>
+        <v>3.821589933837677</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.866521834366906</v>
+        <v>2.86038008405695</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.193979608697074</v>
+        <v>-5.733228744387995</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7885735665743292</v>
+        <v>0.5667321619880048</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.084999607843805</v>
+        <v>-1.521591845926638</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.215522069660623</v>
+        <v>1.947424976500967</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349958</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.867200418284246</v>
+        <v>2.86105866797429</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.078039759071888</v>
+        <v>-5.61728889476281</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8356280903417432</v>
+        <v>0.6137866857554188</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.008177876827681</v>
+        <v>-1.444770114910514</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.262293692187638</v>
+        <v>1.994196599027982</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972339</v>
+        <v>3.848613050972332</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.864198489504239</v>
+        <v>2.858056739194283</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.835384170648725</v>
+        <v>-5.374633306339646</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9296883969310021</v>
+        <v>0.7078469923446775</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.008177876827681</v>
+        <v>-1.444770114910514</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.259291763407631</v>
+        <v>1.991194670247975</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145931</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.865777526514854</v>
+        <v>2.859635776204898</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.615363372611714</v>
+        <v>-5.154612508302636</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.01927575315642</v>
+        <v>0.7974343485700959</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8669580317597012</v>
+        <v>-1.303550269842534</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.345602707459033</v>
+        <v>2.077505614299378</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009942</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.881671709316677</v>
+        <v>2.875529959006721</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.416114742706905</v>
+        <v>-4.955363878397827</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.114869387920167</v>
+        <v>0.893027983333843</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8669580317597012</v>
+        <v>-1.303550269842534</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.361496890260856</v>
+        <v>2.093399797101201</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966251</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.882817553756979</v>
+        <v>2.876675803447023</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.256599639187535</v>
+        <v>-4.795848774878457</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.179821273768217</v>
+        <v>0.9579798691818928</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7074429282403313</v>
+        <v>-1.144035166323164</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.45835179681278</v>
+        <v>2.190254703653125</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046987</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.892905656318419</v>
+        <v>2.886763906008463</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.20864311082244</v>
+        <v>-4.651176629778719</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.209091987675695</v>
+        <v>1.025936829783228</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.6594863998752358</v>
+        <v>-0.9993630212234264</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.497213816393277</v>
+        <v>2.287146093274407</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412094</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.80824534840514</v>
+        <v>2.802103598095184</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.190873651891484</v>
+        <v>-4.633407170847764</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.131539463334799</v>
+        <v>0.9483843054423315</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.6417169409442802</v>
+        <v>-0.9815935622924707</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.423215183838572</v>
+        <v>2.213147460719702</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144507</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.830645841727706</v>
+        <v>2.82450409141775</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.104074154112475</v>
+        <v>-4.546607673068754</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.188659755768969</v>
+        <v>1.005504597876501</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.6417169409442802</v>
+        <v>-0.9815935622924707</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.445615677161138</v>
+        <v>2.235547954042268</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900694</v>
+        <v>3.729142822900686</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.830718243101118</v>
+        <v>2.824576492791163</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.004381539383463</v>
+        <v>-4.446915058339743</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.228609203033986</v>
+        <v>1.045454045141518</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5420243262152684</v>
+        <v>-0.8819009475634589</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.505503647371958</v>
+        <v>2.295435924253087</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.743216620473592</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.84172516557582</v>
+        <v>2.835583415265865</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.072751725707473</v>
+        <v>-4.515285244663753</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.212268050979084</v>
+        <v>1.029112893086616</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.5327486271790535</v>
+        <v>-0.872625248527244</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.522075989268389</v>
+        <v>2.312008266149518</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417556397837</v>
+        <v>3.714175563978361</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.832161874207712</v>
+        <v>2.826020123897756</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.951335296080996</v>
+        <v>-4.393868815037276</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.251271331461566</v>
+        <v>1.068116173569098</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.5327486271790535</v>
+        <v>-0.872625248527244</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.51251269790028</v>
+        <v>2.30244497478141</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887695</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.656871439248099</v>
+        <v>2.650729688938143</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.982328455409702</v>
+        <v>-4.424861974365982</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.063583632770471</v>
+        <v>0.8804284748780027</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.5327486271790535</v>
+        <v>-0.872625248527244</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.337222262940667</v>
+        <v>2.127154539821797</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460389506759</v>
+        <v>3.746038950675892</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.661438671239886</v>
+        <v>2.65529692092993</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.806854195617233</v>
+        <v>-4.249387714573512</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.138340568679246</v>
+        <v>0.9551854107867783</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.5327486271790535</v>
+        <v>-0.872625248527244</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.341789494932454</v>
+        <v>2.131721771813584</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695447</v>
+        <v>3.765020747695438</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.661450145126684</v>
+        <v>2.655308394816728</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.917790448258481</v>
+        <v>-4.360323967214761</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.093977541509544</v>
+        <v>0.9108223836170763</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.5327486271790535</v>
+        <v>-0.872625248527244</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.341800968819252</v>
+        <v>2.131733245700382</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581284</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.664581530346589</v>
+        <v>2.658439780036634</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.120817025801714</v>
+        <v>-4.563350544757994</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.015898295712157</v>
+        <v>0.8327431378196886</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.7357752047222869</v>
+        <v>-1.075651826070477</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.223116407513217</v>
+        <v>2.013048684394347</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.784340376734153</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.674753916778722</v>
+        <v>2.668612166468766</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.962891426866422</v>
+        <v>-4.405424945822701</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.089240921718406</v>
+        <v>0.9060857638259381</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.7357752047222869</v>
+        <v>-1.075651826070477</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.23328879394535</v>
+        <v>2.02322107082648</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212289</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.669700187352582</v>
+        <v>2.663558437042626</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.11121268067755</v>
+        <v>-4.55374619963383</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.024858690767815</v>
+        <v>0.841703532875347</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.7357752047222869</v>
+        <v>-1.075651826070477</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.22823506451921</v>
+        <v>2.01816734140034</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786046</v>
+        <v>3.752023923786037</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.661475962797108</v>
+        <v>2.655334212487152</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.263266639246802</v>
+        <v>-4.649758926454634</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9558128827846395</v>
+        <v>0.7950742175915508</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.8031230842785855</v>
+        <v>-1.100813464398239</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.179602112229956</v>
+        <v>1.994846133848209</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.795480554427088</v>
+        <v>3.438765255187882</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.812318357538788</v>
+        <v>2.584974541744763</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.357928430070483</v>
+        <v>-4.535843083044175</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.068790561196847</v>
+        <v>0.7702808842133455</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.8212407295926045</v>
+        <v>-1.100813464398239</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.319573919783225</v>
+        <v>1.92448646310582</v>
       </c>
     </row>
   </sheetData>
